--- a/resources/items.xlsx
+++ b/resources/items.xlsx
@@ -5,14 +5,20 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="players" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="otherWorld" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="skills" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="ally" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">ally!$A$1:$K$12</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">items!$A$1:$E$6</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">otherWorld!$A$1:$M$60</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">skills!$A$1:$I$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="224">
   <si>
     <t xml:space="preserve">Наименование карты</t>
   </si>
@@ -99,15 +105,613 @@
   </si>
   <si>
     <t xml:space="preserve">PLAYER_00003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Другой мир</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Синий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зеленый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Красный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Желтый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">systemName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">удача</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скорость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">знания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скрытность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сила</t>
+  </si>
+  <si>
+    <t xml:space="preserve">воля</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Абисс (Бездна)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы идете на мерцающий свет. Пройдите проверку Удачи (-1). При успехе сияние укажет путь домой: вернитесь в Аркхэм. При провале это ловушка: появляется монстр!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Удачи (-1), или встретите на своем пути огромную гору с таинственным символом. Этот знак, будто выцарапанный гигантским когтем, заставит мир вокруг вас пошатнуться, и вы потеряете 3 единицы рассудка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Скорости (-1), чтобы ускользнуть от целой стаи чудовищ. При провале вы потеряны во времени и пространстве.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Можете утолить голод светящимися грибами. Если пробуете их, пройдите проверку Удачи (-1). При провале бросьте кубик и потеряйте столько здоровья, сколько выпало. При успехе бросьте кубик и восстановите столько здоровья, сколько выпало.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пещера расходится на рукава. Пройдите проверку Удачи (+1) и сверьтесь с таблицей: Успехи:  0-1 выйдите в Черной пещере. 2 выйдите в Стране снов. 3+ войдите в темный храм; пройдите проверку Удачи (-1), чтобы взять уникальную вещь.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">От слабого света и тепла свечи вы немного пришли в себя. Получите 1 единицу здоровья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каменный свод рушится! Пройдите проверку Скорости (-1), чтобы увернуться от обвала. При провале бросьте кубик и потеряйте столько здоровья, сколько выпало.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Окрестности сбивают вас с толку. Пройдите проверку Знания (-1), или проблуждаете здесь еще один ход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подозрительное эхо беспокоит вас. Пройдите проверку Скрытности (-1), или потеряете 2 единицы рассудка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В кромешной темноте вы сбились с пути. Пройдите проверку Удачи (-2), или потеряете 1 единицу рассудка и останетесь здесь еще на ход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00001_C_00011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы сели перевести дух у пруда со светящейся водой, который кишит черной слепой рыбой. Пройдите проверку Удачи (-1), чтобы заметить в воде необычный предмет. Выловив его, получите 1 Уникальную вещь и $3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Другое Измерение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Блеск золота привлек ваше внимание. Получите $2.		</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мельком увиденный родной дом возвращает вам надежду. Получите 1 единицу рассудка.		</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Появляется отвратительный монстр!		</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Внезапно вас атакует монстр!		</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Появляется монстр!		</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Монстр появляется из теней!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Воздух с треском рвется над вашей головой. Пройдите проверку Знания (-1), чтобы из вашего разума не было выжжено заклинание. При провале сбросьте 1 Заклинание по своему выбору.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гигантский глаз следит за алтарем. Можете пройти проверку Скрытности (-1) и стащить с алтаря свиток. При успехе возьмите 1 Заклинание, при провале потеряйте 3 единицы рассудка от жуткой боли.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удача улыбнулась вам: в тайнике с припасами нашлась 1 Простая вещь.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Повсюду рыщут чудовища. Пройдите проверку Скрытности (-2), или проведете здесь в укрытии весь следующий ход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Силы (-1), чтобы удержать в руках вырываемую ветром добычу: возьмите 1 Заклинание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сдвиньте крышку каменного сундука проверкой Силы (-2). Внутри $8. Провал отнимет у вас 1 единицу здоровья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Силы (-2), чтобы сломать решетку в стене. За ней кроется нечто восхитительное: возьмите 1 Уникальную вещь.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Удачи (-1), чтобы найти древние письмена с ценной информацией о Мифе. Получите 1 Улику за каждый успех в этой проверке.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Удачи (-1) и возьмите 1 Уникальную вещь при успехе.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Удачи (-1), чтобы отыскать важный документ: получите 2 Улики.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Удачи (-1), чтобы найти тихое место для отдыха: получите по 2 единицы здоровья и рассудка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Удачи (-1), чтобы найти средство самообороны. Возьмите из колоды Простых вещей первое попавшееся оружие.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Удачи (-1), чтобы найти врата домой. При успехе тут же вернитесь в Аркхэм.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пройдите проверку Скорости (-1) и подхватите резную доску раньше, чем она упадет. Возьмите 1 Заклинание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неожиданно все, что вы видели, обрело смысл! Получите 1 улику.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неожиданно вы замечаете нечто, ранее ускользавшее от вас. Получите 1 улику.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цвета ослепляют вас. Чтобы не остаться здесь на следующий ход, пройдите проверку Знания (-1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Влажность и жара изматывают вас. Потеряйте 1 единицу здоровья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Безумие этого места наконец поразило вас. Потеряйте 1 единицу рассудка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обсидиановая дверь не хочет открываться. Пройдите проверку Силы (-1), иначе останетесь здесь еще на ход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Розовые лучи едва не задели вас! Пройдите проверку Скрытности (+0), иначе потеряете 2 здоровья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Веревка исчезает далеко наверху, но других путей из расщелины, где вы очутились, не видно. Пройдите проверку Силы (-1), заберитесь наверх и вернитесь в Аркхэм. При провале потеряйте 2 единицы здоровья и останьтесь здесь на следующий ход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сотканное из теней существо бросило погоню, но бегство вымотало вас до предела: потеряйте 1 единицу здоровья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Небо вращается! Пройдите проверку Воли (-2), не то проведете здесь весь следующий ход, борясь с головокружением.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тяготы этого странствия невыносимы. Потеряйте 1 единицу рассудка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нескончаемая чернота устрашает вас. Пройдите проверку Воли (-1), чтобы не потерять 1 единицу рассудка от страха и 1 единицу здоровья от истощения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На этих бесплодных пустошах контакта нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вокруг вас искажаются время и пространство. Пройдите проверку Удачи (-1), чтобы вернуться в Аркхэм, иначе останетесь здесь еще на ход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Под упавшим камнем вы нашли свиток. Возьмите 1 Заклинание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы начинаете понимать местных странных обитателей. Получите 1 Улику.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы заплутали в лабиринте высоких стен. Пройдите проверку Знания (-1), или останетесь бродить здесь на весь следующий ход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Здесь небезопасно... а вот и монстр появился!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы нашли убитую тварь. Пройдите проверку Удачи (-1), чтобы получить 2 улики и трофей-монстра из пула (даже если он неисчислим).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы набрели на спящее чудовище, которое держит в щупальцах золотого идола. Достать статуэтку из объятий существа, не разбудив его, - сложная задача. Пройдите проверку Скрытности (-1). Успех принесет вам $3, а при провале вы потеряете 2 единицы здоровья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы нашли спокойное местечко, где можно передохнуть. Получите 1 единицу здоровья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы нашли ценные предметы, за которые неплохо заплатят в Аркхэме. Получите $3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы выдохлись. Бросьте кубик за каждую имеющуюся единицу здоровья. Провал лишит вас этой единицы, но если вы останетесь в сознании, каждый успех даст одну Улику.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">От крепкого сна вас будит звук вашего голоса, что-то напевающего. Пройдите проверку Удачи (-2). При успехе вы вспомните слова напева, возьмете 1 Заклинание и получите 2 Улики. Иначе пение привлечет других любителей музыки: появляется монстр!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы глядите в лицо безумия. Бросьте кубик за каждую имеющуюся единицу рассудка. Провал лишит вас этой единицы, но если вы не сойдете с ума, каждый успех даст 1 Улику.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дело сделано: пора домой, пока держится портал! Пройдите проверку Скорости (-2) и вернитесь в Аркхэм, иначе вы потеряны во времени и пространстве. Врата, через которые вы входили, в любом случае закрываются.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW_00002_C_00048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Знания переполняют ваш разум. Пройдите проверку Знания (-2). При успехе возьмите 1 Заклинание, но потеряйте 1 единицу рассудка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Навык</t>
+  </si>
+  <si>
+    <t xml:space="preserve">описание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отвага</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В любой фазе: задействуйте эту карту для повторной проверки Ужаса.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оккультист эксперт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В любой фазе: задействуйте эту карту для повторной проверки Заклинания.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сила </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда тратите улику, чтобы получить бонус к проверке Силы, добавляйте еще один бонусный кубик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Знание </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда тратите улику, чтобы получить бонус к проверке Знания, добавляйте еще один бонусный кубик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удача </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда тратите улику, чтобы получить бонус к проверке Удачи, добавляйте еще один бонусный кубик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снайпер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В любой фазе: задействуйте эту карту для повторной проверки Битвы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скрытность </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда тратите улику, чтобы получить бонус к проверке Скрытности, добавляйте еще один бонусный кубик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скорость </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда тратите улику, чтобы получить бонус к проверке Скорости, добавляйте еще один бонусный кубик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Невидимость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В любой фазе: задействуйте эту карту для повторной проверки Ухода.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKILL_00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Воля </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда тратите улику, чтобы получить бонус к проверке Воли, добавляйте еще один бонусный кубик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">рассудок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">здоровье</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анна Каслоу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда к вам присоединяется Анна Каслоу, получите 2 Улики.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Джон Леграссе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вы можете брать монстров с неисчислимостью в качестве трофеев.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дюк</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сбросьте карту Дюка, чтобы тут же восстановить свой рассудок до предела.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Профессор Армитэйдж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваши атаки преодолевают магическое сопротивление, нанося полный урон.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Райан Дин</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда к вам присоединяется Райан Дин, возьмите 1 Простую вещь.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ричард Аптон Пикмэн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваши атаки преодолевают физическое сопротивление, нанося полный урон.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Руби Стэндиш</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда к вам присоединяется Руби Стэндиш, возьмите 1 Уникальную вещь.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сэр Уильям Бринтон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сбросьте карту сэра Уильяма, чтобы восстановить свое здоровье до предела.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Том «Гора» Мерфи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваше здоровье не страдает от сокрушения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Томас Ф. Мэлоун</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда к вам присоединяется Томас Ф. Мэлоун, возьмите 1 Заклинание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLY_00011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эрик Кольт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ваш рассудок не страдает от кошмара.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -174,7 +778,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -189,6 +793,46 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -213,6 +857,18 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -459,10 +1115,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -483,53 +1139,53 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -542,4 +1198,3695 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M160"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="7.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="7.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="6.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="8.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="5.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="136.76"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L25" s="9"/>
+      <c r="M25" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L26" s="9"/>
+      <c r="M26" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L39" s="9"/>
+      <c r="M39" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L41" s="9"/>
+      <c r="M41" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="8"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="8"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="8"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="8"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="8"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8"/>
+      <c r="B87" s="10"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8"/>
+      <c r="B91" s="10"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="8"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="8"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8"/>
+      <c r="B97" s="10"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="10"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="10"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="10"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="8"/>
+      <c r="B103" s="10"/>
+      <c r="C103" s="10"/>
+      <c r="D103" s="10"/>
+      <c r="E103" s="10"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="8"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="8"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="10"/>
+      <c r="D105" s="10"/>
+      <c r="E105" s="10"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="10"/>
+      <c r="D106" s="10"/>
+      <c r="E106" s="10"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="8"/>
+      <c r="B107" s="10"/>
+      <c r="C107" s="10"/>
+      <c r="D107" s="10"/>
+      <c r="E107" s="10"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="8"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="10"/>
+      <c r="D108" s="10"/>
+      <c r="E108" s="10"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="8"/>
+      <c r="B109" s="10"/>
+      <c r="C109" s="10"/>
+      <c r="D109" s="10"/>
+      <c r="E109" s="10"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="8"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="8"/>
+      <c r="B110" s="10"/>
+      <c r="C110" s="10"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="8"/>
+      <c r="B111" s="10"/>
+      <c r="C111" s="10"/>
+      <c r="D111" s="10"/>
+      <c r="E111" s="10"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="8"/>
+      <c r="B112" s="10"/>
+      <c r="C112" s="10"/>
+      <c r="D112" s="10"/>
+      <c r="E112" s="10"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="8"/>
+      <c r="B113" s="10"/>
+      <c r="C113" s="10"/>
+      <c r="D113" s="10"/>
+      <c r="E113" s="10"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="8"/>
+      <c r="B114" s="10"/>
+      <c r="C114" s="10"/>
+      <c r="D114" s="10"/>
+      <c r="E114" s="10"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="8"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="8"/>
+      <c r="L114" s="8"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="8"/>
+      <c r="B115" s="10"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="10"/>
+      <c r="E115" s="10"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="8"/>
+      <c r="B116" s="10"/>
+      <c r="C116" s="10"/>
+      <c r="D116" s="10"/>
+      <c r="E116" s="10"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8"/>
+      <c r="K116" s="8"/>
+      <c r="L116" s="8"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="8"/>
+      <c r="B117" s="10"/>
+      <c r="C117" s="10"/>
+      <c r="D117" s="10"/>
+      <c r="E117" s="10"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8"/>
+      <c r="K117" s="8"/>
+      <c r="L117" s="8"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="8"/>
+      <c r="B118" s="10"/>
+      <c r="C118" s="10"/>
+      <c r="D118" s="10"/>
+      <c r="E118" s="10"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="8"/>
+      <c r="J118" s="8"/>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="8"/>
+      <c r="B119" s="10"/>
+      <c r="C119" s="10"/>
+      <c r="D119" s="10"/>
+      <c r="E119" s="10"/>
+      <c r="F119" s="8"/>
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="8"/>
+      <c r="J119" s="8"/>
+      <c r="K119" s="8"/>
+      <c r="L119" s="8"/>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="8"/>
+      <c r="B120" s="10"/>
+      <c r="C120" s="10"/>
+      <c r="D120" s="10"/>
+      <c r="E120" s="10"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="8"/>
+      <c r="J120" s="8"/>
+      <c r="K120" s="8"/>
+      <c r="L120" s="8"/>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="8"/>
+      <c r="B121" s="10"/>
+      <c r="C121" s="10"/>
+      <c r="D121" s="10"/>
+      <c r="E121" s="10"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="8"/>
+      <c r="J121" s="8"/>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="8"/>
+      <c r="B122" s="10"/>
+      <c r="C122" s="10"/>
+      <c r="D122" s="10"/>
+      <c r="E122" s="10"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="8"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="8"/>
+      <c r="L122" s="8"/>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="8"/>
+      <c r="B123" s="10"/>
+      <c r="C123" s="10"/>
+      <c r="D123" s="10"/>
+      <c r="E123" s="10"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="8"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="8"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="8"/>
+      <c r="L123" s="8"/>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="8"/>
+      <c r="B124" s="10"/>
+      <c r="C124" s="10"/>
+      <c r="D124" s="10"/>
+      <c r="E124" s="10"/>
+      <c r="F124" s="8"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="8"/>
+      <c r="I124" s="8"/>
+      <c r="J124" s="8"/>
+      <c r="K124" s="8"/>
+      <c r="L124" s="8"/>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="8"/>
+      <c r="B125" s="10"/>
+      <c r="C125" s="10"/>
+      <c r="D125" s="10"/>
+      <c r="E125" s="10"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="8"/>
+      <c r="K125" s="8"/>
+      <c r="L125" s="8"/>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="8"/>
+      <c r="B126" s="10"/>
+      <c r="C126" s="10"/>
+      <c r="D126" s="10"/>
+      <c r="E126" s="10"/>
+      <c r="F126" s="8"/>
+      <c r="G126" s="8"/>
+      <c r="H126" s="8"/>
+      <c r="I126" s="8"/>
+      <c r="J126" s="8"/>
+      <c r="K126" s="8"/>
+      <c r="L126" s="8"/>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="8"/>
+      <c r="B127" s="10"/>
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="8"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="8"/>
+      <c r="J127" s="8"/>
+      <c r="K127" s="8"/>
+      <c r="L127" s="8"/>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="8"/>
+      <c r="B128" s="10"/>
+      <c r="C128" s="10"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="8"/>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8"/>
+      <c r="K128" s="8"/>
+      <c r="L128" s="8"/>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="8"/>
+      <c r="B129" s="10"/>
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="10"/>
+      <c r="F129" s="8"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="8"/>
+      <c r="J129" s="8"/>
+      <c r="K129" s="8"/>
+      <c r="L129" s="8"/>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="8"/>
+      <c r="B130" s="10"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="10"/>
+      <c r="E130" s="10"/>
+      <c r="F130" s="8"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="8"/>
+      <c r="L130" s="8"/>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="8"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="8"/>
+      <c r="L131" s="8"/>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="8"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="10"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="8"/>
+      <c r="J132" s="8"/>
+      <c r="K132" s="8"/>
+      <c r="L132" s="8"/>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="8"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="10"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10"/>
+      <c r="F133" s="8"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="8"/>
+      <c r="J133" s="8"/>
+      <c r="K133" s="8"/>
+      <c r="L133" s="8"/>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="8"/>
+      <c r="B134" s="10"/>
+      <c r="C134" s="10"/>
+      <c r="D134" s="10"/>
+      <c r="E134" s="10"/>
+      <c r="F134" s="8"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8"/>
+      <c r="K134" s="8"/>
+      <c r="L134" s="8"/>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="8"/>
+      <c r="B135" s="10"/>
+      <c r="C135" s="10"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="10"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="8"/>
+      <c r="H135" s="8"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8"/>
+      <c r="K135" s="8"/>
+      <c r="L135" s="8"/>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="8"/>
+      <c r="B136" s="10"/>
+      <c r="C136" s="10"/>
+      <c r="D136" s="10"/>
+      <c r="E136" s="10"/>
+      <c r="F136" s="8"/>
+      <c r="G136" s="8"/>
+      <c r="H136" s="8"/>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="8"/>
+      <c r="L136" s="8"/>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="8"/>
+      <c r="B137" s="10"/>
+      <c r="C137" s="10"/>
+      <c r="D137" s="10"/>
+      <c r="E137" s="10"/>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8"/>
+      <c r="K137" s="8"/>
+      <c r="L137" s="8"/>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="8"/>
+      <c r="B138" s="10"/>
+      <c r="C138" s="10"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="8"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="8"/>
+      <c r="J138" s="8"/>
+      <c r="K138" s="8"/>
+      <c r="L138" s="8"/>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="8"/>
+      <c r="B139" s="10"/>
+      <c r="C139" s="10"/>
+      <c r="D139" s="10"/>
+      <c r="E139" s="10"/>
+      <c r="F139" s="8"/>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="8"/>
+      <c r="J139" s="8"/>
+      <c r="K139" s="8"/>
+      <c r="L139" s="8"/>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="8"/>
+      <c r="B140" s="10"/>
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8"/>
+      <c r="K140" s="8"/>
+      <c r="L140" s="8"/>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="8"/>
+      <c r="B141" s="10"/>
+      <c r="C141" s="10"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="10"/>
+      <c r="F141" s="8"/>
+      <c r="G141" s="8"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="8"/>
+      <c r="J141" s="8"/>
+      <c r="K141" s="8"/>
+      <c r="L141" s="8"/>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="8"/>
+      <c r="B142" s="10"/>
+      <c r="C142" s="10"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="8"/>
+      <c r="J142" s="8"/>
+      <c r="K142" s="8"/>
+      <c r="L142" s="8"/>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="8"/>
+      <c r="B143" s="10"/>
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="8"/>
+      <c r="J143" s="8"/>
+      <c r="K143" s="8"/>
+      <c r="L143" s="8"/>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="8"/>
+      <c r="B144" s="10"/>
+      <c r="C144" s="10"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="8"/>
+      <c r="J144" s="8"/>
+      <c r="K144" s="8"/>
+      <c r="L144" s="8"/>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="8"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="8"/>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="8"/>
+      <c r="J145" s="8"/>
+      <c r="K145" s="8"/>
+      <c r="L145" s="8"/>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="8"/>
+      <c r="B146" s="10"/>
+      <c r="C146" s="10"/>
+      <c r="D146" s="10"/>
+      <c r="E146" s="10"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="8"/>
+      <c r="J146" s="8"/>
+      <c r="K146" s="8"/>
+      <c r="L146" s="8"/>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="8"/>
+      <c r="B147" s="10"/>
+      <c r="C147" s="10"/>
+      <c r="D147" s="10"/>
+      <c r="E147" s="10"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="8"/>
+      <c r="J147" s="8"/>
+      <c r="K147" s="8"/>
+      <c r="L147" s="8"/>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="8"/>
+      <c r="B148" s="10"/>
+      <c r="C148" s="10"/>
+      <c r="D148" s="10"/>
+      <c r="E148" s="10"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="8"/>
+      <c r="J148" s="8"/>
+      <c r="K148" s="8"/>
+      <c r="L148" s="8"/>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="8"/>
+      <c r="B149" s="10"/>
+      <c r="C149" s="10"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="10"/>
+      <c r="F149" s="8"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="8"/>
+      <c r="J149" s="8"/>
+      <c r="K149" s="8"/>
+      <c r="L149" s="8"/>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="8"/>
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="8"/>
+      <c r="G150" s="8"/>
+      <c r="H150" s="8"/>
+      <c r="I150" s="8"/>
+      <c r="J150" s="8"/>
+      <c r="K150" s="8"/>
+      <c r="L150" s="8"/>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="8"/>
+      <c r="B151" s="10"/>
+      <c r="C151" s="10"/>
+      <c r="D151" s="10"/>
+      <c r="E151" s="10"/>
+      <c r="F151" s="8"/>
+      <c r="G151" s="8"/>
+      <c r="H151" s="8"/>
+      <c r="I151" s="8"/>
+      <c r="J151" s="8"/>
+      <c r="K151" s="8"/>
+      <c r="L151" s="8"/>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="8"/>
+      <c r="B152" s="10"/>
+      <c r="C152" s="10"/>
+      <c r="D152" s="10"/>
+      <c r="E152" s="10"/>
+      <c r="F152" s="8"/>
+      <c r="G152" s="8"/>
+      <c r="H152" s="8"/>
+      <c r="I152" s="8"/>
+      <c r="J152" s="8"/>
+      <c r="K152" s="8"/>
+      <c r="L152" s="8"/>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="8"/>
+      <c r="B153" s="10"/>
+      <c r="C153" s="10"/>
+      <c r="D153" s="10"/>
+      <c r="E153" s="10"/>
+      <c r="F153" s="8"/>
+      <c r="G153" s="8"/>
+      <c r="H153" s="8"/>
+      <c r="I153" s="8"/>
+      <c r="J153" s="8"/>
+      <c r="K153" s="8"/>
+      <c r="L153" s="8"/>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="8"/>
+      <c r="B154" s="10"/>
+      <c r="C154" s="10"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="10"/>
+      <c r="F154" s="8"/>
+      <c r="G154" s="8"/>
+      <c r="H154" s="8"/>
+      <c r="I154" s="8"/>
+      <c r="J154" s="8"/>
+      <c r="K154" s="8"/>
+      <c r="L154" s="8"/>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="8"/>
+      <c r="B155" s="10"/>
+      <c r="C155" s="10"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="8"/>
+      <c r="G155" s="8"/>
+      <c r="H155" s="8"/>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8"/>
+      <c r="K155" s="8"/>
+      <c r="L155" s="8"/>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="8"/>
+      <c r="B156" s="10"/>
+      <c r="C156" s="10"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="10"/>
+      <c r="F156" s="8"/>
+      <c r="G156" s="8"/>
+      <c r="H156" s="8"/>
+      <c r="I156" s="8"/>
+      <c r="J156" s="8"/>
+      <c r="K156" s="8"/>
+      <c r="L156" s="8"/>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="8"/>
+      <c r="B157" s="10"/>
+      <c r="C157" s="10"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="10"/>
+      <c r="F157" s="8"/>
+      <c r="G157" s="8"/>
+      <c r="H157" s="8"/>
+      <c r="I157" s="8"/>
+      <c r="J157" s="8"/>
+      <c r="K157" s="8"/>
+      <c r="L157" s="8"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="8"/>
+      <c r="B158" s="10"/>
+      <c r="C158" s="10"/>
+      <c r="D158" s="10"/>
+      <c r="E158" s="10"/>
+      <c r="F158" s="8"/>
+      <c r="G158" s="8"/>
+      <c r="H158" s="8"/>
+      <c r="I158" s="8"/>
+      <c r="J158" s="8"/>
+      <c r="K158" s="8"/>
+      <c r="L158" s="8"/>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="8"/>
+      <c r="B159" s="10"/>
+      <c r="C159" s="10"/>
+      <c r="D159" s="10"/>
+      <c r="E159" s="10"/>
+      <c r="F159" s="8"/>
+      <c r="G159" s="8"/>
+      <c r="H159" s="8"/>
+      <c r="I159" s="8"/>
+      <c r="J159" s="8"/>
+      <c r="K159" s="8"/>
+      <c r="L159" s="8"/>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="8"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="8"/>
+      <c r="G160" s="8"/>
+      <c r="H160" s="8"/>
+      <c r="I160" s="8"/>
+      <c r="J160" s="8"/>
+      <c r="K160" s="8"/>
+      <c r="L160" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M60"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="85.84"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I11"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="67.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="13" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K12"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/resources/items.xlsx
+++ b/resources/items.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" state="visible" r:id="rId3"/>
@@ -4722,9 +4722,16 @@
       <c r="B2" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
       <c r="K2" s="1" t="s">
         <v>193</v>
       </c>
@@ -4736,9 +4743,16 @@
       <c r="B3" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
       <c r="K3" s="1" t="s">
         <v>196</v>
       </c>
@@ -4750,9 +4764,16 @@
       <c r="B4" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="I4" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="9"/>
       <c r="K4" s="1" t="s">
         <v>199</v>
       </c>
@@ -4764,9 +4785,16 @@
       <c r="B5" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
       <c r="K5" s="1" t="s">
         <v>202</v>
       </c>
@@ -4778,12 +4806,18 @@
       <c r="B6" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
       <c r="K6" s="1" t="s">
         <v>205</v>
       </c>
@@ -4795,12 +4829,18 @@
       <c r="B7" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="C7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
       <c r="K7" s="1" t="s">
         <v>208</v>
       </c>
@@ -4812,9 +4852,16 @@
       <c r="B8" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
       <c r="K8" s="1" t="s">
         <v>211</v>
       </c>
@@ -4826,7 +4873,14 @@
       <c r="B9" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -4840,9 +4894,16 @@
       <c r="B10" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
       <c r="K10" s="1" t="s">
         <v>217</v>
       </c>
@@ -4854,12 +4915,18 @@
       <c r="B11" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
       <c r="K11" s="1" t="s">
         <v>220</v>
       </c>
@@ -4871,9 +4938,16 @@
       <c r="B12" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
       <c r="K12" s="1" t="s">
         <v>223</v>
       </c>

--- a/resources/items.xlsx
+++ b/resources/items.xlsx
@@ -124,31 +124,31 @@
     <t xml:space="preserve">Улика</t>
   </si>
   <si>
-    <t xml:space="preserve">Diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Square</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triangle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexagon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crescent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slash</t>
+    <t xml:space="preserve">♦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■</t>
+  </si>
+  <si>
+    <t xml:space="preserve">●</t>
+  </si>
+  <si>
+    <t xml:space="preserve">▲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⬢</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/</t>
   </si>
   <si>
     <t xml:space="preserve">Описание</t>
@@ -1675,7 +1675,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O176"/>
+  <dimension ref="A1:S176"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.3"/>
@@ -1683,19 +1683,20 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="7.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="4.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="4.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="4.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="4.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="5.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="110.46"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="6" customFormat="true" ht="23.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>25</v>
       </c>
@@ -1741,6 +1742,10 @@
       <c r="O1" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="0"/>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
@@ -1776,6 +1781,7 @@
       <c r="O2" s="8" t="s">
         <v>45</v>
       </c>
+      <c r="P2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -1811,6 +1817,7 @@
       <c r="O3" s="8" t="s">
         <v>51</v>
       </c>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
@@ -1848,6 +1855,7 @@
       <c r="O4" s="8" t="s">
         <v>57</v>
       </c>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
@@ -1881,6 +1889,7 @@
       <c r="O5" s="8" t="s">
         <v>62</v>
       </c>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
@@ -1914,6 +1923,7 @@
       <c r="O6" s="8" t="s">
         <v>65</v>
       </c>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
@@ -1951,6 +1961,7 @@
       <c r="O7" s="8" t="s">
         <v>69</v>
       </c>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
@@ -1986,6 +1997,7 @@
       <c r="O8" s="8" t="s">
         <v>74</v>
       </c>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
@@ -2021,6 +2033,7 @@
       <c r="O9" s="8" t="s">
         <v>77</v>
       </c>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
@@ -2058,6 +2071,7 @@
       <c r="O10" s="8" t="s">
         <v>80</v>
       </c>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
@@ -2093,6 +2107,7 @@
       <c r="O11" s="8" t="s">
         <v>83</v>
       </c>
+      <c r="P11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
@@ -2130,6 +2145,7 @@
       <c r="O12" s="8" t="s">
         <v>86</v>
       </c>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
@@ -2167,6 +2183,7 @@
       <c r="O13" s="8" t="s">
         <v>89</v>
       </c>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
@@ -2200,6 +2217,7 @@
       <c r="O14" s="8" t="s">
         <v>92</v>
       </c>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
@@ -2235,6 +2253,7 @@
       <c r="O15" s="8" t="s">
         <v>95</v>
       </c>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
@@ -2270,6 +2289,7 @@
       <c r="O16" s="8" t="s">
         <v>99</v>
       </c>
+      <c r="P16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
@@ -2303,6 +2323,7 @@
       <c r="O17" s="8" t="s">
         <v>102</v>
       </c>
+      <c r="P17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
@@ -2336,6 +2357,7 @@
       <c r="O18" s="8" t="s">
         <v>105</v>
       </c>
+      <c r="P18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
@@ -2371,6 +2393,7 @@
       <c r="O19" s="8" t="s">
         <v>108</v>
       </c>
+      <c r="P19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
@@ -2404,6 +2427,7 @@
       <c r="O20" s="8" t="s">
         <v>111</v>
       </c>
+      <c r="P20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
@@ -2437,6 +2461,7 @@
       <c r="O21" s="8" t="s">
         <v>114</v>
       </c>
+      <c r="P21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
@@ -2470,6 +2495,7 @@
       <c r="O22" s="8" t="s">
         <v>117</v>
       </c>
+      <c r="P22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
@@ -2505,6 +2531,7 @@
       <c r="O23" s="8" t="s">
         <v>120</v>
       </c>
+      <c r="P23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
@@ -2538,6 +2565,7 @@
       <c r="O24" s="8" t="s">
         <v>123</v>
       </c>
+      <c r="P24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
@@ -2575,6 +2603,7 @@
       <c r="O25" s="8" t="s">
         <v>126</v>
       </c>
+      <c r="P25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
@@ -2610,6 +2639,7 @@
       <c r="O26" s="8" t="s">
         <v>129</v>
       </c>
+      <c r="P26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
@@ -2647,6 +2677,7 @@
       <c r="O27" s="11" t="s">
         <v>132</v>
       </c>
+      <c r="P27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
@@ -2664,6 +2695,7 @@
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
       <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
@@ -2681,6 +2713,7 @@
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
       <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
@@ -2698,6 +2731,7 @@
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
       <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
@@ -2715,6 +2749,7 @@
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
       <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
@@ -2732,6 +2767,7 @@
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
       <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
@@ -2749,6 +2785,7 @@
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
       <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
@@ -2766,6 +2803,7 @@
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
       <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
@@ -2783,6 +2821,7 @@
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
       <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
@@ -2800,6 +2839,7 @@
       <c r="M36" s="9"/>
       <c r="N36" s="9"/>
       <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
@@ -2817,6 +2857,7 @@
       <c r="M37" s="9"/>
       <c r="N37" s="9"/>
       <c r="O37" s="8"/>
+      <c r="P37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
@@ -2834,6 +2875,7 @@
       <c r="M38" s="9"/>
       <c r="N38" s="9"/>
       <c r="O38" s="8"/>
+      <c r="P38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
@@ -2851,6 +2893,7 @@
       <c r="M39" s="9"/>
       <c r="N39" s="9"/>
       <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
@@ -2868,6 +2911,7 @@
       <c r="M40" s="9"/>
       <c r="N40" s="9"/>
       <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
@@ -2885,6 +2929,7 @@
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
       <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7"/>
@@ -2902,6 +2947,7 @@
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
       <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7"/>
@@ -2919,6 +2965,7 @@
       <c r="M43" s="9"/>
       <c r="N43" s="9"/>
       <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7"/>
@@ -2936,6 +2983,7 @@
       <c r="M44" s="9"/>
       <c r="N44" s="9"/>
       <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7"/>
@@ -2953,6 +3001,7 @@
       <c r="M45" s="9"/>
       <c r="N45" s="9"/>
       <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7"/>
@@ -2970,6 +3019,7 @@
       <c r="M46" s="9"/>
       <c r="N46" s="9"/>
       <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7"/>
@@ -2987,6 +3037,7 @@
       <c r="M47" s="9"/>
       <c r="N47" s="9"/>
       <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7"/>
@@ -3004,6 +3055,7 @@
       <c r="M48" s="9"/>
       <c r="N48" s="9"/>
       <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
@@ -3021,6 +3073,7 @@
       <c r="M49" s="9"/>
       <c r="N49" s="9"/>
       <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
@@ -3038,6 +3091,7 @@
       <c r="M50" s="9"/>
       <c r="N50" s="9"/>
       <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
@@ -3055,6 +3109,7 @@
       <c r="M51" s="9"/>
       <c r="N51" s="9"/>
       <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
@@ -3072,6 +3127,7 @@
       <c r="M52" s="9"/>
       <c r="N52" s="9"/>
       <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
@@ -3089,6 +3145,7 @@
       <c r="M53" s="9"/>
       <c r="N53" s="9"/>
       <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
@@ -3106,6 +3163,7 @@
       <c r="M54" s="9"/>
       <c r="N54" s="9"/>
       <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
@@ -3123,6 +3181,7 @@
       <c r="M55" s="9"/>
       <c r="N55" s="9"/>
       <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
@@ -3140,6 +3199,7 @@
       <c r="M56" s="9"/>
       <c r="N56" s="9"/>
       <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
@@ -3157,6 +3217,7 @@
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
       <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
@@ -3174,6 +3235,7 @@
       <c r="M58" s="9"/>
       <c r="N58" s="9"/>
       <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
@@ -3191,6 +3253,7 @@
       <c r="M59" s="9"/>
       <c r="N59" s="9"/>
       <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
@@ -3208,6 +3271,7 @@
       <c r="M60" s="9"/>
       <c r="N60" s="9"/>
       <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
@@ -3225,6 +3289,7 @@
       <c r="M61" s="9"/>
       <c r="N61" s="9"/>
       <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
@@ -3242,6 +3307,7 @@
       <c r="M62" s="9"/>
       <c r="N62" s="9"/>
       <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
@@ -3259,6 +3325,7 @@
       <c r="M63" s="9"/>
       <c r="N63" s="9"/>
       <c r="O63" s="8"/>
+      <c r="P63" s="8"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
@@ -3276,6 +3343,7 @@
       <c r="M64" s="9"/>
       <c r="N64" s="9"/>
       <c r="O64" s="8"/>
+      <c r="P64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
@@ -3293,6 +3361,7 @@
       <c r="M65" s="9"/>
       <c r="N65" s="9"/>
       <c r="O65" s="8"/>
+      <c r="P65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
@@ -3310,6 +3379,7 @@
       <c r="M66" s="9"/>
       <c r="N66" s="9"/>
       <c r="O66" s="8"/>
+      <c r="P66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
@@ -3327,6 +3397,7 @@
       <c r="M67" s="9"/>
       <c r="N67" s="9"/>
       <c r="O67" s="8"/>
+      <c r="P67" s="8"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
@@ -3344,6 +3415,7 @@
       <c r="M68" s="9"/>
       <c r="N68" s="9"/>
       <c r="O68" s="8"/>
+      <c r="P68" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
@@ -3361,6 +3433,7 @@
       <c r="M69" s="9"/>
       <c r="N69" s="9"/>
       <c r="O69" s="8"/>
+      <c r="P69" s="8"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
@@ -3378,6 +3451,7 @@
       <c r="M70" s="9"/>
       <c r="N70" s="9"/>
       <c r="O70" s="8"/>
+      <c r="P70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
@@ -3395,6 +3469,7 @@
       <c r="M71" s="9"/>
       <c r="N71" s="9"/>
       <c r="O71" s="8"/>
+      <c r="P71" s="8"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
@@ -3412,6 +3487,7 @@
       <c r="M72" s="9"/>
       <c r="N72" s="9"/>
       <c r="O72" s="8"/>
+      <c r="P72" s="8"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
@@ -3429,6 +3505,7 @@
       <c r="M73" s="9"/>
       <c r="N73" s="9"/>
       <c r="O73" s="8"/>
+      <c r="P73" s="8"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
@@ -3446,6 +3523,7 @@
       <c r="M74" s="9"/>
       <c r="N74" s="9"/>
       <c r="O74" s="8"/>
+      <c r="P74" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
@@ -3463,6 +3541,7 @@
       <c r="M75" s="9"/>
       <c r="N75" s="9"/>
       <c r="O75" s="8"/>
+      <c r="P75" s="8"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
@@ -3480,6 +3559,7 @@
       <c r="M76" s="9"/>
       <c r="N76" s="9"/>
       <c r="O76" s="8"/>
+      <c r="P76" s="8"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
@@ -3497,6 +3577,7 @@
       <c r="M77" s="9"/>
       <c r="N77" s="9"/>
       <c r="O77" s="8"/>
+      <c r="P77" s="8"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
@@ -3514,6 +3595,7 @@
       <c r="M78" s="9"/>
       <c r="N78" s="9"/>
       <c r="O78" s="8"/>
+      <c r="P78" s="8"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
@@ -3531,6 +3613,7 @@
       <c r="M79" s="9"/>
       <c r="N79" s="9"/>
       <c r="O79" s="8"/>
+      <c r="P79" s="8"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
@@ -3548,6 +3631,7 @@
       <c r="M80" s="9"/>
       <c r="N80" s="9"/>
       <c r="O80" s="8"/>
+      <c r="P80" s="8"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
@@ -3565,6 +3649,7 @@
       <c r="M81" s="9"/>
       <c r="N81" s="9"/>
       <c r="O81" s="8"/>
+      <c r="P81" s="8"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
@@ -3582,6 +3667,7 @@
       <c r="M82" s="9"/>
       <c r="N82" s="9"/>
       <c r="O82" s="8"/>
+      <c r="P82" s="8"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
@@ -3599,6 +3685,7 @@
       <c r="M83" s="9"/>
       <c r="N83" s="9"/>
       <c r="O83" s="8"/>
+      <c r="P83" s="8"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7"/>
@@ -3616,6 +3703,7 @@
       <c r="M84" s="9"/>
       <c r="N84" s="9"/>
       <c r="O84" s="8"/>
+      <c r="P84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7"/>
@@ -3633,6 +3721,7 @@
       <c r="M85" s="9"/>
       <c r="N85" s="9"/>
       <c r="O85" s="8"/>
+      <c r="P85" s="8"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7"/>
@@ -3650,6 +3739,7 @@
       <c r="M86" s="9"/>
       <c r="N86" s="9"/>
       <c r="O86" s="12"/>
+      <c r="P86" s="12"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7"/>

--- a/resources/items.xlsx
+++ b/resources/items.xlsx
@@ -1692,7 +1692,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="4.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="5.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="110.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="96.88"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -1743,9 +1743,9 @@
         <v>39</v>
       </c>
       <c r="P1" s="4"/>
-      <c r="Q1" s="0"/>
-      <c r="R1" s="0"/>
-      <c r="S1" s="0"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>75</v>
       </c>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="P14" s="8"/>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="47.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
         <v>93</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="69.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
         <v>96</v>
       </c>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
         <v>127</v>
       </c>

--- a/resources/items.xlsx
+++ b/resources/items.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">ally!$A$1:$K$12</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">items!$A$1:$E$6</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">myth!$A$1:$O$6</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">myth!$A$1:$O$66</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">otherWorld!$A$1:$M$60</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">skills!$A$1:$I$11</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="449">
   <si>
     <t xml:space="preserve">Наименование карты</t>
   </si>
@@ -431,6 +431,360 @@
   </si>
   <si>
     <t xml:space="preserve">Благодаря процветанию, постигшему Аркхэм, уровень ужаса не может повыситься.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наступление жары</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверки Силы в Аркхэме облагаются штрафом -1.  Проверки Знания в Аркхэме получают бонус +1.  Стойкость огненных вампиров увеличивается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кошмар из котлована!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ложа Серебряных Сумерек</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Строители потревожили древний камень, и на улицы Университета Мискатоник вышли два монстра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гололедица</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В фазе Движения сыщики получают на 1 единицу движения меньше обычного.  Быстрые монстры движутся как обычные монстры.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неудачи преследуют Аркхэм!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый игрок должен пройти проверку Удачи (-1), иначе будет Проклят.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Член Ложи задержан для допроса!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ритуал Серебряной Ложи выпустил на улицы Фрэнч Хилл двух монстров.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Члены Ложи во всеоружии!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех монстров с улиц и из локаций Фрэнч Хилл.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Охота за головами в Аркхэме!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех монстров из локаций.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Торговцы вышли на бой с преступностью!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех монстров с улиц и из локаций Торгового района.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Возвращение Мискатоникской арктической экспедиции!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Любой Старейшина, ранее взятый как трофей, оживает и выходит в речном порту.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пропавшие люди вернулись!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Все сыщики, которые на данный момент потеряны во времени и пространстве, могут тут же вернуться на любую улицу или в любую локацию Аркхэма по своему выбору.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теперь никто не сможет вам помочь…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Врата не могут быть запечатаны, хотя закрывать их все еще можно.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снисхождение Ноденса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запечатать врата стоит на 2 Улики меньше обычного.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Паника на пикнике!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Беспечные отдыхающие выманили двух монстров на улицы Даунтауна.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парад планет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мистическая энергия от взаимного расположения небесных тел снижает до 0 цену могущества всех Заклинаний.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Полиция патрулирует Нортсайд!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех монстров с улиц и из локаций Нортсайда.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В Аптауне нанимают частною охрану!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех монстров с улиц и из локаций Аптауна.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дождь как из ведра</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверки Скорости в Аркхэме облагаются штрафом -1. В фазе Движения каждый сыщик получает на 1 единицу движения меньше обычного.  Проверки Скрытности в Аркхэме получают бонус +1.  Если в игре есть огненные вампиры, верните всех их в пул. Если огненный вампир входит в игру, сразу верните его в пул и вытяните другого монстра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жители Ривертауна вернули себе контроль над районом!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех монстров с улиц и из локаций Ривертауна.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Возвышение Р'лиэха</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стойкость звездных отродий и маньяков увеличивается на 1. Сложность закрытия или запечатывания врат на Р'лиэх увеличивается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ученые предупреждают о межпространственном проколе!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех Бродящих меж миров и Псов Тиндалоса из Аркхэма. Если в пул вернулся хотя бы один монстр, уровень ужаса повышается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Банда Шелдона бежит за помощью к полиции!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Банда Шелдона разрыла погребальный курган, выпустив двух монстров на улицы Аптауна.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Убийства в трущобах продолжаются!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старый подвал открылся, и из него на улицы Исттауна вылезли два монстра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Солнечное затмение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Из-за солнечного затмения нельзя применять Заклинания.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Саутсайдский душитель пойман!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Между тем, пресса заблуждается: в убийствах повинны два монстра, которые появились на улицах Саутсайда.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Странные огни в кампусе!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">До конца следующего раунда закрыты Библиотека, Здание Администрации и Дом Науки. Оставьте эту карту в игре, чтобы не забыть об этом обстоятельстве.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Город страдает от необъяснимых скачков напряжения!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Все сыщики в Иных мирах могут немедленно вернуться в Аркхэм.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Солнечно и ясно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверки Скрытности в Аркхэме облагаются штрафом -1.  Проверки Воли в Аркхэме получают бонус +1.  Если Населяющий тьму в игре, верните его в пул. Если Населяющий тьму входит в игру, сразу верните его в пул и вытяните другого монстра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В городе эпидемия трезвости!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждый сыщик, у которого есть карта «Виски», должен пройти проверку Скрытности (-1), иначе будет арестован и доставлен в полицейский участок. Если это произойдет, сыщик обязан сбросить «Виски». До конца следующего раунда закрывается Забегаловка Гиббса. Оставьте эту карту в игре, чтобы не забыть об этом.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ужас на вокзале!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проржавевший поезд прибыл в Аркхэм, и с него на улицы Нортсайда сошли два монстра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Могильный холод</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стойкость всей нежити увеличивается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фестиваль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стойкость культистов и бьяхи увеличивается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Великий ритуал</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Развитие: стойкость культистов, ведьм, колдунов и высших жрецов увеличивается на 2. В конце каждой фазы Мифа, начиная со следующего раунда, кладите на эту карту 1 Улику.  Опровержение: если в фазе контактов в Аркхэме любой сыщик сбросит на Фрэнч Хилл 3 Заклинания (4, если игроков больше пяти), уберите эту карту в коробку. Каждый сыщик получает по 2 Улики.  Подтверждение: как только на этой карте накопится 5 Улик, уберите ее в коробку. С этого момента в каждой фазе Мифа берите по 2 карты. На первой взятой игнорируйте все, кроме открытия врат.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Человек в черном</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Сыщики, закончившие движение на Фрэнч Хилл, могут заключить сделку с Человеком в черном. За каждую имеющуюся у него единицу Рассудка сыщик бросает кубик. Каждый провал лишает его этой единицы. Если сыщик таким образом потеряет весь рассудок, он сожран; в противном случае он берет 1 Заклинание и получает 1 Улику.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Саутсайдсций душитель наносит удар</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Развитие: в конце каждой фазы Мифа, начиная со следующего раунда, убирайте в коробку одну каргу из колоды Союзников.  Опровержение: если любой игрок в фазе контактов в Аркхэме сбросит 5 Улик в Пансионате Мамаши, уберите эту карту в коробку. Каждый игрок получает $5 награды от полиции.  Подтверждение: если в конце фазы Мифа в колоде Союзников не осталось карт, уберите эту карту в коробку. Каждый сыщик понижает на единицу предел Здоровья или Рассудка (по выбору игрока) до конца игры.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расположение звезд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Развитие: бросайте кубик в конце каждой фазы Мифа, начиная со следующего раунда. При результате 1 или 2 положите на трек Древнего 1 жетон Безысходности.  Опровержение: если в фазе контактов в Аркхэме любой сыщик сбросит Союзника в Даунтауне, уберите эту карту в коробку. Каждый сыщик получает по 2 Простые вещи.  Подтверждение: уберите эту карту в коробку, если Древний проснулся.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жуткий эксперимент</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда эта карта входит в игру, положите на нее 5 монстров из пула. Они не двигаются и не идут в счет лимита. В фазе контактов в Аркхэме любой сыщик на улицах университета может биться с одним или несколькими из этих монстров по своему выбору. При победе сыщик берет трофеи.  Развитие: в конце каждой фазы Мифа, начиная со следующего раунда, кладите на эту карту одного монстра из пула.  Опровержение: если на этой карте не осталось монстров, уберите ее в коробку. Каждый сыщик берет 1 Навык.  Подтверждение: если на этой карте 8 монстров, поднимите уровень ужаса до 10, выведите монстров с нее на улицы университета и уберите карту в коробку.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Создания тьмы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стойкость всех вурдалаков, бесформенных тварей, шогготов и летучих полипов увеличивается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бдительные граждане на страже порядка!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верните в пул всех монстров с улиц и из локаций Даунтауна.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYTH_00065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Годовщина coжжения ведьм!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Древнее проклятие накрыло Аркхэм. На улицы Ривертауна вышли два монстра.</t>
   </si>
   <si>
     <t xml:space="preserve">Другой мир</t>
@@ -1148,7 +1502,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1194,6 +1548,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2679,706 +3037,1400 @@
       </c>
       <c r="P27" s="11"/>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="8"/>
+      <c r="O28" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="P28" s="8"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+    <row r="29" customFormat="false" ht="24.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
+      <c r="L29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N29" s="9"/>
-      <c r="O29" s="8"/>
+      <c r="O29" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="P29" s="8"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+    <row r="30" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
+      <c r="L30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="N30" s="9"/>
-      <c r="O30" s="8"/>
+      <c r="O30" s="8" t="s">
+        <v>142</v>
+      </c>
       <c r="P30" s="8"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
+      <c r="I31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="8"/>
+      <c r="N31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>145</v>
+      </c>
       <c r="P31" s="8"/>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="J32" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="8"/>
+      <c r="O32" s="8" t="s">
+        <v>148</v>
+      </c>
       <c r="P32" s="8"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
+      <c r="J33" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="8"/>
+      <c r="O33" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="P33" s="8"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
+      <c r="I34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="8"/>
+      <c r="N34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="P34" s="8"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="8"/>
+      <c r="O35" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="P35" s="8"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
+    <row r="36" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
+      <c r="L36" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="8"/>
+      <c r="N36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="P36" s="8"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
+      <c r="I37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="8"/>
+      <c r="N37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="P37" s="8"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
+      <c r="L38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" s="9"/>
-      <c r="O38" s="8"/>
+      <c r="O38" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="P38" s="8"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
+      <c r="I39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="8"/>
+      <c r="N39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>169</v>
+      </c>
       <c r="P39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
+      <c r="A40" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
+      <c r="L40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N40" s="9"/>
-      <c r="O40" s="8"/>
+      <c r="O40" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="P40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
+      <c r="A41" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
-      <c r="O41" s="8"/>
+      <c r="O41" s="8" t="s">
+        <v>175</v>
+      </c>
       <c r="P41" s="8"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
-      <c r="O42" s="8"/>
+      <c r="O42" s="8" t="s">
+        <v>178</v>
+      </c>
       <c r="P42" s="8"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
       <c r="M43" s="9"/>
       <c r="N43" s="9"/>
-      <c r="O43" s="8"/>
+      <c r="O43" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="P43" s="8"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
+    <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
+      <c r="L44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="N44" s="9"/>
-      <c r="O44" s="8"/>
+      <c r="O44" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="P44" s="8"/>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
+    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I45" s="9"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
       <c r="N45" s="9"/>
-      <c r="O45" s="8"/>
+      <c r="O45" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="P45" s="8"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+    <row r="46" customFormat="false" ht="24.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
+      <c r="I46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-      <c r="O46" s="8"/>
+      <c r="M46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="8" t="s">
+        <v>190</v>
+      </c>
       <c r="P46" s="8"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
+    <row r="47" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
+      <c r="I47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="L47" s="9"/>
       <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-      <c r="O47" s="8"/>
+      <c r="N47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8" t="s">
+        <v>193</v>
+      </c>
       <c r="P47" s="8"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
+    <row r="48" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
       <c r="M48" s="9"/>
       <c r="N48" s="9"/>
-      <c r="O48" s="8"/>
+      <c r="O48" s="8" t="s">
+        <v>196</v>
+      </c>
       <c r="P48" s="8"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
+      <c r="L49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N49" s="9"/>
-      <c r="O49" s="8"/>
+      <c r="O49" s="8" t="s">
+        <v>199</v>
+      </c>
       <c r="P49" s="8"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
       <c r="N50" s="9"/>
-      <c r="O50" s="8"/>
+      <c r="O50" s="8" t="s">
+        <v>202</v>
+      </c>
       <c r="P50" s="8"/>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
       <c r="M51" s="9"/>
       <c r="N51" s="9"/>
-      <c r="O51" s="8"/>
+      <c r="O51" s="8" t="s">
+        <v>205</v>
+      </c>
       <c r="P51" s="8"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
+      <c r="I52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-      <c r="O52" s="8"/>
+      <c r="M52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>208</v>
+      </c>
       <c r="P52" s="8"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
+      <c r="I53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9"/>
-      <c r="O53" s="8"/>
+      <c r="M53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="s">
+        <v>211</v>
+      </c>
       <c r="P53" s="8"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
+      <c r="L54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="N54" s="9"/>
-      <c r="O54" s="8"/>
+      <c r="O54" s="8" t="s">
+        <v>214</v>
+      </c>
       <c r="P54" s="8"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="I55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="9"/>
-      <c r="O55" s="8"/>
+      <c r="M55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>217</v>
+      </c>
       <c r="P55" s="8"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
+    <row r="56" customFormat="false" ht="21.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
       <c r="I56" s="9"/>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
+      <c r="L56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N56" s="9"/>
-      <c r="O56" s="8"/>
+      <c r="O56" s="8" t="s">
+        <v>220</v>
+      </c>
       <c r="P56" s="8"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
+      <c r="A57" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="9"/>
+      <c r="L57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="N57" s="9"/>
-      <c r="O57" s="8"/>
+      <c r="O57" s="8" t="s">
+        <v>223</v>
+      </c>
       <c r="P57" s="8"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
       <c r="J58" s="9"/>
       <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
+      <c r="L58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="N58" s="9"/>
-      <c r="O58" s="8"/>
+      <c r="O58" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="P58" s="8"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
+    <row r="59" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="E59" s="8"/>
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
+      <c r="I59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9"/>
-      <c r="O59" s="8"/>
+      <c r="M59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="8" t="s">
+        <v>229</v>
+      </c>
       <c r="P59" s="8"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+    <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
+      <c r="L60" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="N60" s="9"/>
-      <c r="O60" s="8"/>
+      <c r="O60" s="8" t="s">
+        <v>232</v>
+      </c>
       <c r="P60" s="8"/>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
+    <row r="61" customFormat="false" ht="71.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="E61" s="8"/>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
+      <c r="I61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" s="9"/>
       <c r="L61" s="9"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="9"/>
-      <c r="O61" s="8"/>
+      <c r="M61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="s">
+        <v>235</v>
+      </c>
       <c r="P61" s="8"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
+    <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="E62" s="8"/>
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9"/>
+      <c r="I62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" s="9"/>
       <c r="L62" s="9"/>
-      <c r="M62" s="9"/>
-      <c r="N62" s="9"/>
-      <c r="O62" s="8"/>
+      <c r="M62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="8" t="s">
+        <v>238</v>
+      </c>
       <c r="P62" s="8"/>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
+    <row r="63" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="E63" s="8"/>
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
+      <c r="I63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" s="9"/>
       <c r="L63" s="9"/>
-      <c r="M63" s="9"/>
-      <c r="N63" s="9"/>
-      <c r="O63" s="8"/>
+      <c r="M63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="8" t="s">
+        <v>241</v>
+      </c>
       <c r="P63" s="8"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
       <c r="L64" s="9"/>
       <c r="M64" s="9"/>
       <c r="N64" s="9"/>
-      <c r="O64" s="8"/>
+      <c r="O64" s="8" t="s">
+        <v>244</v>
+      </c>
       <c r="P64" s="8"/>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
       <c r="L65" s="9"/>
       <c r="M65" s="9"/>
       <c r="N65" s="9"/>
-      <c r="O65" s="8"/>
+      <c r="O65" s="8" t="s">
+        <v>247</v>
+      </c>
       <c r="P65" s="8"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
       <c r="J66" s="9"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="9"/>
-      <c r="M66" s="9"/>
+      <c r="L66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N66" s="9"/>
-      <c r="O66" s="8"/>
+      <c r="O66" s="8" t="s">
+        <v>250</v>
+      </c>
       <c r="P66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3738,8 +4790,8 @@
       <c r="L86" s="9"/>
       <c r="M86" s="9"/>
       <c r="N86" s="9"/>
-      <c r="O86" s="12"/>
-      <c r="P86" s="12"/>
+      <c r="O86" s="13"/>
+      <c r="P86" s="13"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7"/>
@@ -4496,10 +5548,10 @@
       <c r="N135" s="9"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="12"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12"/>
-      <c r="E136" s="12"/>
+      <c r="B136" s="13"/>
+      <c r="C136" s="13"/>
+      <c r="D136" s="13"/>
+      <c r="E136" s="13"/>
       <c r="F136" s="9"/>
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
@@ -4511,10 +5563,10 @@
       <c r="N136" s="9"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="12"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12"/>
-      <c r="E137" s="12"/>
+      <c r="B137" s="13"/>
+      <c r="C137" s="13"/>
+      <c r="D137" s="13"/>
+      <c r="E137" s="13"/>
       <c r="F137" s="9"/>
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
@@ -4526,10 +5578,10 @@
       <c r="N137" s="9"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="12"/>
-      <c r="C138" s="12"/>
-      <c r="D138" s="12"/>
-      <c r="E138" s="12"/>
+      <c r="B138" s="13"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
       <c r="F138" s="9"/>
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
@@ -4541,10 +5593,10 @@
       <c r="N138" s="9"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="12"/>
-      <c r="C139" s="12"/>
-      <c r="D139" s="12"/>
-      <c r="E139" s="12"/>
+      <c r="B139" s="13"/>
+      <c r="C139" s="13"/>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
       <c r="F139" s="9"/>
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
@@ -4556,10 +5608,10 @@
       <c r="N139" s="9"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="12"/>
-      <c r="C140" s="12"/>
-      <c r="D140" s="12"/>
-      <c r="E140" s="12"/>
+      <c r="B140" s="13"/>
+      <c r="C140" s="13"/>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
       <c r="F140" s="9"/>
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
@@ -4571,10 +5623,10 @@
       <c r="N140" s="9"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="12"/>
-      <c r="C141" s="12"/>
-      <c r="D141" s="12"/>
-      <c r="E141" s="12"/>
+      <c r="B141" s="13"/>
+      <c r="C141" s="13"/>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
       <c r="F141" s="9"/>
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
@@ -4586,10 +5638,10 @@
       <c r="N141" s="9"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="12"/>
-      <c r="C142" s="12"/>
-      <c r="D142" s="12"/>
-      <c r="E142" s="12"/>
+      <c r="B142" s="13"/>
+      <c r="C142" s="13"/>
+      <c r="D142" s="13"/>
+      <c r="E142" s="13"/>
       <c r="F142" s="9"/>
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
@@ -4601,10 +5653,10 @@
       <c r="N142" s="9"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="12"/>
-      <c r="C143" s="12"/>
-      <c r="D143" s="12"/>
-      <c r="E143" s="12"/>
+      <c r="B143" s="13"/>
+      <c r="C143" s="13"/>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
       <c r="F143" s="9"/>
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
@@ -4616,10 +5668,10 @@
       <c r="N143" s="9"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="12"/>
-      <c r="C144" s="12"/>
-      <c r="D144" s="12"/>
-      <c r="E144" s="12"/>
+      <c r="B144" s="13"/>
+      <c r="C144" s="13"/>
+      <c r="D144" s="13"/>
+      <c r="E144" s="13"/>
       <c r="F144" s="9"/>
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
@@ -4631,10 +5683,10 @@
       <c r="N144" s="9"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="12"/>
-      <c r="C145" s="12"/>
-      <c r="D145" s="12"/>
-      <c r="E145" s="12"/>
+      <c r="B145" s="13"/>
+      <c r="C145" s="13"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
       <c r="F145" s="9"/>
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
@@ -4646,10 +5698,10 @@
       <c r="N145" s="9"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="12"/>
-      <c r="C146" s="12"/>
-      <c r="D146" s="12"/>
-      <c r="E146" s="12"/>
+      <c r="B146" s="13"/>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
       <c r="F146" s="9"/>
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
@@ -4661,10 +5713,10 @@
       <c r="N146" s="9"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="12"/>
-      <c r="C147" s="12"/>
-      <c r="D147" s="12"/>
-      <c r="E147" s="12"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
       <c r="F147" s="9"/>
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
@@ -4676,10 +5728,10 @@
       <c r="N147" s="9"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="12"/>
-      <c r="C148" s="12"/>
-      <c r="D148" s="12"/>
-      <c r="E148" s="12"/>
+      <c r="B148" s="13"/>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
       <c r="F148" s="9"/>
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
@@ -4691,10 +5743,10 @@
       <c r="N148" s="9"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="12"/>
-      <c r="C149" s="12"/>
-      <c r="D149" s="12"/>
-      <c r="E149" s="12"/>
+      <c r="B149" s="13"/>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
       <c r="F149" s="9"/>
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
@@ -4706,10 +5758,10 @@
       <c r="N149" s="9"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="12"/>
-      <c r="C150" s="12"/>
-      <c r="D150" s="12"/>
-      <c r="E150" s="12"/>
+      <c r="B150" s="13"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
       <c r="F150" s="9"/>
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
@@ -4721,10 +5773,10 @@
       <c r="N150" s="9"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="12"/>
-      <c r="C151" s="12"/>
-      <c r="D151" s="12"/>
-      <c r="E151" s="12"/>
+      <c r="B151" s="13"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="9"/>
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
@@ -4736,10 +5788,10 @@
       <c r="N151" s="9"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="12"/>
-      <c r="C152" s="12"/>
-      <c r="D152" s="12"/>
-      <c r="E152" s="12"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
       <c r="F152" s="9"/>
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
@@ -4751,151 +5803,151 @@
       <c r="N152" s="9"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="12"/>
-      <c r="C153" s="12"/>
-      <c r="D153" s="12"/>
-      <c r="E153" s="12"/>
+      <c r="B153" s="13"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="13"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="12"/>
-      <c r="C154" s="12"/>
-      <c r="D154" s="12"/>
-      <c r="E154" s="12"/>
+      <c r="B154" s="13"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="13"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="12"/>
-      <c r="C155" s="12"/>
-      <c r="D155" s="12"/>
-      <c r="E155" s="12"/>
+      <c r="B155" s="13"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="13"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="12"/>
-      <c r="C156" s="12"/>
-      <c r="D156" s="12"/>
-      <c r="E156" s="12"/>
+      <c r="B156" s="13"/>
+      <c r="C156" s="13"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="13"/>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="12"/>
-      <c r="C157" s="12"/>
-      <c r="D157" s="12"/>
-      <c r="E157" s="12"/>
+      <c r="B157" s="13"/>
+      <c r="C157" s="13"/>
+      <c r="D157" s="13"/>
+      <c r="E157" s="13"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="12"/>
-      <c r="C158" s="12"/>
-      <c r="D158" s="12"/>
-      <c r="E158" s="12"/>
+      <c r="B158" s="13"/>
+      <c r="C158" s="13"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="13"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="12"/>
-      <c r="C159" s="12"/>
-      <c r="D159" s="12"/>
-      <c r="E159" s="12"/>
+      <c r="B159" s="13"/>
+      <c r="C159" s="13"/>
+      <c r="D159" s="13"/>
+      <c r="E159" s="13"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="12"/>
-      <c r="C160" s="12"/>
-      <c r="D160" s="12"/>
-      <c r="E160" s="12"/>
+      <c r="B160" s="13"/>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="12"/>
-      <c r="C161" s="12"/>
-      <c r="D161" s="12"/>
-      <c r="E161" s="12"/>
+      <c r="B161" s="13"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="13"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="12"/>
-      <c r="C162" s="12"/>
-      <c r="D162" s="12"/>
-      <c r="E162" s="12"/>
+      <c r="B162" s="13"/>
+      <c r="C162" s="13"/>
+      <c r="D162" s="13"/>
+      <c r="E162" s="13"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="12"/>
-      <c r="C163" s="12"/>
-      <c r="D163" s="12"/>
-      <c r="E163" s="12"/>
+      <c r="B163" s="13"/>
+      <c r="C163" s="13"/>
+      <c r="D163" s="13"/>
+      <c r="E163" s="13"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="12"/>
-      <c r="C164" s="12"/>
-      <c r="D164" s="12"/>
-      <c r="E164" s="12"/>
+      <c r="B164" s="13"/>
+      <c r="C164" s="13"/>
+      <c r="D164" s="13"/>
+      <c r="E164" s="13"/>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="12"/>
-      <c r="C165" s="12"/>
-      <c r="D165" s="12"/>
-      <c r="E165" s="12"/>
+      <c r="B165" s="13"/>
+      <c r="C165" s="13"/>
+      <c r="D165" s="13"/>
+      <c r="E165" s="13"/>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="12"/>
-      <c r="C166" s="12"/>
-      <c r="D166" s="12"/>
-      <c r="E166" s="12"/>
+      <c r="B166" s="13"/>
+      <c r="C166" s="13"/>
+      <c r="D166" s="13"/>
+      <c r="E166" s="13"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="12"/>
-      <c r="C167" s="12"/>
-      <c r="D167" s="12"/>
-      <c r="E167" s="12"/>
+      <c r="B167" s="13"/>
+      <c r="C167" s="13"/>
+      <c r="D167" s="13"/>
+      <c r="E167" s="13"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="12"/>
-      <c r="C168" s="12"/>
-      <c r="D168" s="12"/>
-      <c r="E168" s="12"/>
+      <c r="B168" s="13"/>
+      <c r="C168" s="13"/>
+      <c r="D168" s="13"/>
+      <c r="E168" s="13"/>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="12"/>
-      <c r="C169" s="12"/>
-      <c r="D169" s="12"/>
-      <c r="E169" s="12"/>
+      <c r="B169" s="13"/>
+      <c r="C169" s="13"/>
+      <c r="D169" s="13"/>
+      <c r="E169" s="13"/>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="12"/>
-      <c r="C170" s="12"/>
-      <c r="D170" s="12"/>
-      <c r="E170" s="12"/>
+      <c r="B170" s="13"/>
+      <c r="C170" s="13"/>
+      <c r="D170" s="13"/>
+      <c r="E170" s="13"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="12"/>
-      <c r="C171" s="12"/>
-      <c r="D171" s="12"/>
-      <c r="E171" s="12"/>
+      <c r="B171" s="13"/>
+      <c r="C171" s="13"/>
+      <c r="D171" s="13"/>
+      <c r="E171" s="13"/>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="12"/>
-      <c r="C172" s="12"/>
-      <c r="D172" s="12"/>
-      <c r="E172" s="12"/>
+      <c r="B172" s="13"/>
+      <c r="C172" s="13"/>
+      <c r="D172" s="13"/>
+      <c r="E172" s="13"/>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="12"/>
-      <c r="C173" s="12"/>
-      <c r="D173" s="12"/>
-      <c r="E173" s="12"/>
+      <c r="B173" s="13"/>
+      <c r="C173" s="13"/>
+      <c r="D173" s="13"/>
+      <c r="E173" s="13"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="12"/>
-      <c r="C174" s="12"/>
-      <c r="D174" s="12"/>
-      <c r="E174" s="12"/>
+      <c r="B174" s="13"/>
+      <c r="C174" s="13"/>
+      <c r="D174" s="13"/>
+      <c r="E174" s="13"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="12"/>
-      <c r="C175" s="12"/>
-      <c r="D175" s="12"/>
-      <c r="E175" s="12"/>
+      <c r="B175" s="13"/>
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="13"/>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="12"/>
-      <c r="C176" s="12"/>
-      <c r="D176" s="12"/>
-      <c r="E176" s="12"/>
+      <c r="B176" s="13"/>
+      <c r="C176" s="13"/>
+      <c r="D176" s="13"/>
+      <c r="E176" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O66"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4916,10 +5968,10 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="7.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="7.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="6.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="8.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="7.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="7.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="6.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="8.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.33"/>
@@ -4932,59 +5984,59 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>137</v>
+        <v>251</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>255</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>139</v>
+        <v>257</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>143</v>
+        <v>261</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>145</v>
+      <c r="A2" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="15" t="s">
-        <v>146</v>
+      <c r="E2" s="17"/>
+      <c r="F2" s="16" t="s">
+        <v>264</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>-1</v>
@@ -4994,24 +6046,24 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
-      <c r="M2" s="17" t="s">
-        <v>147</v>
+      <c r="M2" s="18" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
-        <v>145</v>
+      <c r="A3" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="16"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="15" t="s">
-        <v>148</v>
+      <c r="E3" s="17"/>
+      <c r="F3" s="16" t="s">
+        <v>266</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>-1</v>
@@ -5021,24 +6073,24 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="17" t="s">
-        <v>149</v>
+      <c r="M3" s="18" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
-        <v>145</v>
+      <c r="A4" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="16"/>
+      <c r="C4" s="17"/>
       <c r="D4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="15" t="s">
-        <v>150</v>
+      <c r="E4" s="17"/>
+      <c r="F4" s="16" t="s">
+        <v>268</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="n">
@@ -5048,24 +6100,24 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="17" t="s">
-        <v>151</v>
+      <c r="M4" s="18" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>145</v>
+      <c r="A5" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="16"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="15" t="s">
-        <v>152</v>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16" t="s">
+        <v>270</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-1</v>
@@ -5075,24 +6127,24 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="17" t="s">
-        <v>153</v>
+      <c r="M5" s="18" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>145</v>
+      <c r="A6" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="16"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="15" t="s">
-        <v>154</v>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16" t="s">
+        <v>272</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
@@ -5102,24 +6154,24 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
-      <c r="M6" s="17" t="s">
-        <v>155</v>
+      <c r="M6" s="18" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>145</v>
+      <c r="A7" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="16"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="15" t="s">
-        <v>156</v>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16" t="s">
+        <v>274</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -5127,24 +6179,24 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="17" t="s">
-        <v>157</v>
+      <c r="M7" s="18" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>145</v>
+      <c r="A8" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="16"/>
+      <c r="C8" s="17"/>
       <c r="D8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="15" t="s">
-        <v>158</v>
+      <c r="E8" s="17"/>
+      <c r="F8" s="16" t="s">
+        <v>276</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="n">
@@ -5154,24 +6206,24 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="17" t="s">
-        <v>159</v>
+      <c r="M8" s="18" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>145</v>
+      <c r="A9" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="16"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="15" t="s">
-        <v>160</v>
+      <c r="E9" s="17"/>
+      <c r="F9" s="16" t="s">
+        <v>278</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -5181,24 +6233,24 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="17" t="s">
-        <v>161</v>
+      <c r="M9" s="18" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>145</v>
+      <c r="A10" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="15" t="s">
-        <v>162</v>
+      <c r="E10" s="17"/>
+      <c r="F10" s="16" t="s">
+        <v>280</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -5208,24 +6260,24 @@
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="17" t="s">
-        <v>163</v>
+      <c r="M10" s="18" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>145</v>
+      <c r="A11" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="15" t="s">
-        <v>164</v>
+      <c r="E11" s="17"/>
+      <c r="F11" s="16" t="s">
+        <v>282</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-2</v>
@@ -5235,24 +6287,24 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="17" t="s">
-        <v>165</v>
+      <c r="M11" s="18" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>145</v>
+      <c r="A12" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="15" t="s">
-        <v>166</v>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16" t="s">
+        <v>284</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>-1</v>
@@ -5262,13 +6314,13 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="17" t="s">
-        <v>167</v>
+      <c r="M12" s="18" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>168</v>
+      <c r="A13" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>1</v>
@@ -5282,8 +6334,8 @@
       <c r="E13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>169</v>
+      <c r="F13" s="16" t="s">
+        <v>287</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -5292,12 +6344,12 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="1" t="s">
-        <v>170</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>168</v>
+      <c r="A14" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>1</v>
@@ -5311,8 +6363,8 @@
       <c r="E14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>171</v>
+      <c r="F14" s="16" t="s">
+        <v>289</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -5321,12 +6373,12 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="1" t="s">
-        <v>172</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>168</v>
+      <c r="A15" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>1</v>
@@ -5340,8 +6392,8 @@
       <c r="E15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>173</v>
+      <c r="F15" s="16" t="s">
+        <v>291</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -5350,12 +6402,12 @@
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="1" t="s">
-        <v>174</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>168</v>
+      <c r="A16" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>1</v>
@@ -5369,8 +6421,8 @@
       <c r="E16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>175</v>
+      <c r="F16" s="16" t="s">
+        <v>293</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -5379,12 +6431,12 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="1" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>168</v>
+      <c r="A17" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B17" s="7" t="n">
         <v>1</v>
@@ -5398,8 +6450,8 @@
       <c r="E17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>177</v>
+      <c r="F17" s="16" t="s">
+        <v>295</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -5408,12 +6460,12 @@
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="1" t="s">
-        <v>178</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>168</v>
+      <c r="A18" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>1</v>
@@ -5427,8 +6479,8 @@
       <c r="E18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>179</v>
+      <c r="F18" s="16" t="s">
+        <v>297</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -5437,12 +6489,12 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="1" t="s">
-        <v>178</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>168</v>
+      <c r="A19" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>1</v>
@@ -5456,8 +6508,8 @@
       <c r="E19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>180</v>
+      <c r="F19" s="16" t="s">
+        <v>298</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -5466,12 +6518,12 @@
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="1" t="s">
-        <v>181</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>168</v>
+      <c r="A20" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>1</v>
@@ -5485,8 +6537,8 @@
       <c r="E20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>182</v>
+      <c r="F20" s="16" t="s">
+        <v>300</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -5497,12 +6549,12 @@
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="1" t="s">
-        <v>183</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>168</v>
+      <c r="A21" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>1</v>
@@ -5516,8 +6568,8 @@
       <c r="E21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>184</v>
+      <c r="F21" s="16" t="s">
+        <v>302</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -5528,12 +6580,12 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="1" t="s">
-        <v>185</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>168</v>
+      <c r="A22" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>1</v>
@@ -5547,8 +6599,8 @@
       <c r="E22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>186</v>
+      <c r="F22" s="16" t="s">
+        <v>304</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -5557,12 +6609,12 @@
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="1" t="s">
-        <v>187</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>168</v>
+      <c r="A23" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>1</v>
@@ -5576,8 +6628,8 @@
       <c r="E23" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>188</v>
+      <c r="F23" s="16" t="s">
+        <v>306</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -5588,12 +6640,12 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="1" t="s">
-        <v>189</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>168</v>
+      <c r="A24" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>1</v>
@@ -5607,8 +6659,8 @@
       <c r="E24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>190</v>
+      <c r="F24" s="16" t="s">
+        <v>308</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -5619,12 +6671,12 @@
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="1" t="s">
-        <v>191</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>168</v>
+      <c r="A25" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>1</v>
@@ -5638,8 +6690,8 @@
       <c r="E25" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>192</v>
+      <c r="F25" s="16" t="s">
+        <v>310</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -5650,12 +6702,12 @@
       </c>
       <c r="L25" s="7"/>
       <c r="M25" s="1" t="s">
-        <v>193</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>168</v>
+      <c r="A26" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>1</v>
@@ -5669,8 +6721,8 @@
       <c r="E26" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="15" t="s">
-        <v>194</v>
+      <c r="F26" s="16" t="s">
+        <v>312</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -5681,12 +6733,12 @@
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="1" t="s">
-        <v>195</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>168</v>
+      <c r="A27" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>1</v>
@@ -5700,8 +6752,8 @@
       <c r="E27" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="15" t="s">
-        <v>196</v>
+      <c r="F27" s="16" t="s">
+        <v>314</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>-1</v>
@@ -5712,12 +6764,12 @@
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
       <c r="M27" s="1" t="s">
-        <v>197</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>168</v>
+      <c r="A28" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>1</v>
@@ -5731,8 +6783,8 @@
       <c r="E28" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>198</v>
+      <c r="F28" s="16" t="s">
+        <v>316</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>-1</v>
@@ -5743,12 +6795,12 @@
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
       <c r="M28" s="1" t="s">
-        <v>199</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>168</v>
+      <c r="A29" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>1</v>
@@ -5762,8 +6814,8 @@
       <c r="E29" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>200</v>
+      <c r="F29" s="16" t="s">
+        <v>318</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>-1</v>
@@ -5774,12 +6826,12 @@
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
       <c r="M29" s="1" t="s">
-        <v>201</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>168</v>
+      <c r="A30" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>1</v>
@@ -5793,8 +6845,8 @@
       <c r="E30" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>202</v>
+      <c r="F30" s="16" t="s">
+        <v>320</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>-1</v>
@@ -5805,12 +6857,12 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="M30" s="1" t="s">
-        <v>203</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>168</v>
+      <c r="A31" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>1</v>
@@ -5824,8 +6876,8 @@
       <c r="E31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>204</v>
+      <c r="F31" s="16" t="s">
+        <v>322</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>-1</v>
@@ -5836,12 +6888,12 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c r="M31" s="1" t="s">
-        <v>205</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>168</v>
+      <c r="A32" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>1</v>
@@ -5855,8 +6907,8 @@
       <c r="E32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="15" t="s">
-        <v>206</v>
+      <c r="F32" s="16" t="s">
+        <v>324</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>-1</v>
@@ -5867,12 +6919,12 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="1" t="s">
-        <v>207</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>168</v>
+      <c r="A33" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>1</v>
@@ -5886,8 +6938,8 @@
       <c r="E33" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="15" t="s">
-        <v>208</v>
+      <c r="F33" s="16" t="s">
+        <v>326</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7" t="n">
@@ -5898,12 +6950,12 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="1" t="s">
-        <v>209</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>168</v>
+      <c r="A34" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B34" s="7" t="n">
         <v>1</v>
@@ -5917,8 +6969,8 @@
       <c r="E34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="15" t="s">
-        <v>210</v>
+      <c r="F34" s="16" t="s">
+        <v>328</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
@@ -5927,12 +6979,12 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="1" t="s">
-        <v>211</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
-        <v>168</v>
+      <c r="A35" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>1</v>
@@ -5946,8 +6998,8 @@
       <c r="E35" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="15" t="s">
-        <v>212</v>
+      <c r="F35" s="16" t="s">
+        <v>330</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -5956,12 +7008,12 @@
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="M35" s="1" t="s">
-        <v>213</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>168</v>
+      <c r="A36" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>1</v>
@@ -5975,8 +7027,8 @@
       <c r="E36" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>214</v>
+      <c r="F36" s="16" t="s">
+        <v>332</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
@@ -5987,12 +7039,12 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="1" t="s">
-        <v>215</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>168</v>
+      <c r="A37" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B37" s="7" t="n">
         <v>1</v>
@@ -6006,8 +7058,8 @@
       <c r="E37" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="15" t="s">
-        <v>216</v>
+      <c r="F37" s="16" t="s">
+        <v>334</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
@@ -6016,12 +7068,12 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="1" t="s">
-        <v>217</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>168</v>
+      <c r="A38" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B38" s="7" t="n">
         <v>1</v>
@@ -6035,8 +7087,8 @@
       <c r="E38" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="15" t="s">
-        <v>218</v>
+      <c r="F38" s="16" t="s">
+        <v>336</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
@@ -6045,12 +7097,12 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="1" t="s">
-        <v>219</v>
+        <v>337</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
-        <v>168</v>
+      <c r="A39" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B39" s="7" t="n">
         <v>1</v>
@@ -6064,8 +7116,8 @@
       <c r="E39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="15" t="s">
-        <v>220</v>
+      <c r="F39" s="16" t="s">
+        <v>338</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
@@ -6076,12 +7128,12 @@
       </c>
       <c r="L39" s="7"/>
       <c r="M39" s="1" t="s">
-        <v>221</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>168</v>
+      <c r="A40" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>1</v>
@@ -6095,8 +7147,8 @@
       <c r="E40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="15" t="s">
-        <v>222</v>
+      <c r="F40" s="16" t="s">
+        <v>340</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -6107,12 +7159,12 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c r="M40" s="1" t="s">
-        <v>223</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>168</v>
+      <c r="A41" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>1</v>
@@ -6126,8 +7178,8 @@
       <c r="E41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="15" t="s">
-        <v>224</v>
+      <c r="F41" s="16" t="s">
+        <v>342</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -6138,12 +7190,12 @@
       </c>
       <c r="L41" s="7"/>
       <c r="M41" s="1" t="s">
-        <v>225</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
-        <v>168</v>
+      <c r="A42" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>1</v>
@@ -6157,8 +7209,8 @@
       <c r="E42" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="15" t="s">
-        <v>226</v>
+      <c r="F42" s="16" t="s">
+        <v>344</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -6167,12 +7219,12 @@
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c r="M42" s="1" t="s">
-        <v>227</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>168</v>
+      <c r="A43" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>1</v>
@@ -6186,8 +7238,8 @@
       <c r="E43" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="15" t="s">
-        <v>228</v>
+      <c r="F43" s="16" t="s">
+        <v>346</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -6198,12 +7250,12 @@
         <v>-2</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>229</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
-        <v>168</v>
+      <c r="A44" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>1</v>
@@ -6217,8 +7269,8 @@
       <c r="E44" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="15" t="s">
-        <v>230</v>
+      <c r="F44" s="16" t="s">
+        <v>348</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -6227,12 +7279,12 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="1" t="s">
-        <v>231</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
-        <v>168</v>
+      <c r="A45" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B45" s="7" t="n">
         <v>1</v>
@@ -6246,8 +7298,8 @@
       <c r="E45" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="15" t="s">
-        <v>232</v>
+      <c r="F45" s="16" t="s">
+        <v>350</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
@@ -6258,12 +7310,12 @@
         <v>-1</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>233</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15" t="s">
-        <v>168</v>
+      <c r="A46" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B46" s="7" t="n">
         <v>1</v>
@@ -6277,8 +7329,8 @@
       <c r="E46" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="15" t="s">
-        <v>234</v>
+      <c r="F46" s="16" t="s">
+        <v>352</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -6287,12 +7339,12 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="1" t="s">
-        <v>235</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
-        <v>168</v>
+      <c r="A47" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B47" s="7" t="n">
         <v>1</v>
@@ -6306,8 +7358,8 @@
       <c r="E47" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="15" t="s">
-        <v>236</v>
+      <c r="F47" s="16" t="s">
+        <v>354</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>-1</v>
@@ -6318,12 +7370,12 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="1" t="s">
-        <v>237</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
-        <v>168</v>
+      <c r="A48" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B48" s="7" t="n">
         <v>1</v>
@@ -6337,8 +7389,8 @@
       <c r="E48" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="15" t="s">
-        <v>238</v>
+      <c r="F48" s="16" t="s">
+        <v>356</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -6347,12 +7399,12 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="1" t="s">
-        <v>239</v>
+        <v>357</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
-        <v>168</v>
+      <c r="A49" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B49" s="7" t="n">
         <v>1</v>
@@ -6366,8 +7418,8 @@
       <c r="E49" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="15" t="s">
-        <v>240</v>
+      <c r="F49" s="16" t="s">
+        <v>358</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -6376,12 +7428,12 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c r="M49" s="1" t="s">
-        <v>241</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15" t="s">
-        <v>168</v>
+      <c r="A50" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B50" s="7" t="n">
         <v>1</v>
@@ -6395,8 +7447,8 @@
       <c r="E50" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="15" t="s">
-        <v>242</v>
+      <c r="F50" s="16" t="s">
+        <v>360</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -6407,12 +7459,12 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c r="M50" s="1" t="s">
-        <v>243</v>
+        <v>361</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15" t="s">
-        <v>168</v>
+      <c r="A51" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B51" s="7" t="n">
         <v>1</v>
@@ -6426,8 +7478,8 @@
       <c r="E51" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="15" t="s">
-        <v>244</v>
+      <c r="F51" s="16" t="s">
+        <v>362</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -6436,12 +7488,12 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c r="M51" s="1" t="s">
-        <v>245</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>168</v>
+      <c r="A52" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B52" s="7" t="n">
         <v>1</v>
@@ -6455,8 +7507,8 @@
       <c r="E52" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="15" t="s">
-        <v>246</v>
+      <c r="F52" s="16" t="s">
+        <v>364</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>-1</v>
@@ -6467,12 +7519,12 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="1" t="s">
-        <v>247</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
-        <v>168</v>
+      <c r="A53" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B53" s="7" t="n">
         <v>1</v>
@@ -6486,8 +7538,8 @@
       <c r="E53" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="15" t="s">
-        <v>248</v>
+      <c r="F53" s="16" t="s">
+        <v>366</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
@@ -6498,12 +7550,12 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="1" t="s">
-        <v>249</v>
+        <v>367</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
-        <v>168</v>
+      <c r="A54" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B54" s="7" t="n">
         <v>1</v>
@@ -6517,8 +7569,8 @@
       <c r="E54" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="15" t="s">
-        <v>250</v>
+      <c r="F54" s="16" t="s">
+        <v>368</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -6527,12 +7579,12 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="1" t="s">
-        <v>251</v>
+        <v>369</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15" t="s">
-        <v>168</v>
+      <c r="A55" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B55" s="7" t="n">
         <v>1</v>
@@ -6546,8 +7598,8 @@
       <c r="E55" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="15" t="s">
-        <v>252</v>
+      <c r="F55" s="16" t="s">
+        <v>370</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -6556,12 +7608,12 @@
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c r="M55" s="1" t="s">
-        <v>253</v>
+        <v>371</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15" t="s">
-        <v>168</v>
+      <c r="A56" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B56" s="7" t="n">
         <v>1</v>
@@ -6575,8 +7627,8 @@
       <c r="E56" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="15" t="s">
-        <v>254</v>
+      <c r="F56" s="16" t="s">
+        <v>372</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -6585,12 +7637,12 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c r="M56" s="1" t="s">
-        <v>255</v>
+        <v>373</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15" t="s">
-        <v>168</v>
+      <c r="A57" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B57" s="7" t="n">
         <v>1</v>
@@ -6604,8 +7656,8 @@
       <c r="E57" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="15" t="s">
-        <v>256</v>
+      <c r="F57" s="16" t="s">
+        <v>374</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>-2</v>
@@ -6616,12 +7668,12 @@
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c r="M57" s="1" t="s">
-        <v>257</v>
+        <v>375</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
-        <v>168</v>
+      <c r="A58" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B58" s="7" t="n">
         <v>1</v>
@@ -6635,8 +7687,8 @@
       <c r="E58" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="15" t="s">
-        <v>258</v>
+      <c r="F58" s="16" t="s">
+        <v>376</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -6645,12 +7697,12 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c r="M58" s="1" t="s">
-        <v>259</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15" t="s">
-        <v>168</v>
+      <c r="A59" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B59" s="7" t="n">
         <v>1</v>
@@ -6664,8 +7716,8 @@
       <c r="E59" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="15" t="s">
-        <v>260</v>
+      <c r="F59" s="16" t="s">
+        <v>378</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7" t="n">
@@ -6676,12 +7728,12 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c r="M59" s="1" t="s">
-        <v>261</v>
+        <v>379</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
-        <v>168</v>
+      <c r="A60" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="B60" s="7" t="n">
         <v>1</v>
@@ -6695,8 +7747,8 @@
       <c r="E60" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="15" t="s">
-        <v>262</v>
+      <c r="F60" s="16" t="s">
+        <v>380</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -6707,1408 +7759,1408 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c r="M60" s="1" t="s">
-        <v>263</v>
+        <v>381</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="16"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="15"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="16"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="15"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
+      <c r="A64" s="16"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="16"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="15"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="16"/>
+      <c r="K65" s="16"/>
+      <c r="L65" s="16"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
+      <c r="A66" s="16"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="16"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="15"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="16"/>
+      <c r="J68" s="16"/>
+      <c r="K68" s="16"/>
+      <c r="L68" s="16"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="15"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="15"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="15"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
+      <c r="A71" s="16"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="15"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
+      <c r="A72" s="16"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="15"/>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
+      <c r="A73" s="16"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="15"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="15"/>
-      <c r="K74" s="15"/>
-      <c r="L74" s="15"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="15"/>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
+      <c r="A75" s="16"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="16"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="15"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
-      <c r="L76" s="15"/>
+      <c r="A76" s="16"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
+      <c r="A77" s="16"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="15"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
-      <c r="L78" s="15"/>
+      <c r="A78" s="16"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="16"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="15"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
-      <c r="L79" s="15"/>
+      <c r="A79" s="16"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="15"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
+      <c r="A80" s="16"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="16"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="15"/>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="16"/>
+      <c r="J81" s="16"/>
+      <c r="K81" s="16"/>
+      <c r="L81" s="16"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="15"/>
-      <c r="B82" s="16"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="15"/>
-      <c r="K82" s="15"/>
-      <c r="L82" s="15"/>
+      <c r="A82" s="16"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="16"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="16"/>
+      <c r="J82" s="16"/>
+      <c r="K82" s="16"/>
+      <c r="L82" s="16"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="15"/>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="15"/>
-      <c r="K83" s="15"/>
-      <c r="L83" s="15"/>
+      <c r="A83" s="16"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="16"/>
+      <c r="K83" s="16"/>
+      <c r="L83" s="16"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="15"/>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="15"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="15"/>
-      <c r="K84" s="15"/>
-      <c r="L84" s="15"/>
+      <c r="A84" s="16"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
+      <c r="J84" s="16"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="16"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="15"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16"/>
-      <c r="E85" s="16"/>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="15"/>
-      <c r="K85" s="15"/>
-      <c r="L85" s="15"/>
+      <c r="A85" s="16"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="16"/>
+      <c r="H85" s="16"/>
+      <c r="I85" s="16"/>
+      <c r="J85" s="16"/>
+      <c r="K85" s="16"/>
+      <c r="L85" s="16"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="15"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="15"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="15"/>
-      <c r="K86" s="15"/>
-      <c r="L86" s="15"/>
+      <c r="A86" s="16"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="16"/>
+      <c r="I86" s="16"/>
+      <c r="J86" s="16"/>
+      <c r="K86" s="16"/>
+      <c r="L86" s="16"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="15"/>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="15"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
-      <c r="L87" s="15"/>
+      <c r="A87" s="16"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
+      <c r="I87" s="16"/>
+      <c r="J87" s="16"/>
+      <c r="K87" s="16"/>
+      <c r="L87" s="16"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="15"/>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="15"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="15"/>
-      <c r="K88" s="15"/>
-      <c r="L88" s="15"/>
+      <c r="A88" s="16"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="16"/>
+      <c r="I88" s="16"/>
+      <c r="J88" s="16"/>
+      <c r="K88" s="16"/>
+      <c r="L88" s="16"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15"/>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="15"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="15"/>
-      <c r="K89" s="15"/>
-      <c r="L89" s="15"/>
+      <c r="A89" s="16"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="16"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+      <c r="L89" s="16"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="15"/>
-      <c r="B90" s="16"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="15"/>
-      <c r="K90" s="15"/>
-      <c r="L90" s="15"/>
+      <c r="A90" s="16"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="16"/>
+      <c r="H90" s="16"/>
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="16"/>
+      <c r="L90" s="16"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="15"/>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="15"/>
-      <c r="K91" s="15"/>
-      <c r="L91" s="15"/>
+      <c r="A91" s="16"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="15"/>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="15"/>
+      <c r="A92" s="16"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+      <c r="K92" s="16"/>
+      <c r="L92" s="16"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="15"/>
-      <c r="B93" s="16"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="16"/>
-      <c r="E93" s="16"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="15"/>
+      <c r="A93" s="16"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="17"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="16"/>
+      <c r="H93" s="16"/>
+      <c r="I93" s="16"/>
+      <c r="J93" s="16"/>
+      <c r="K93" s="16"/>
+      <c r="L93" s="16"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="15"/>
-      <c r="B94" s="16"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="16"/>
-      <c r="E94" s="16"/>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="15"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="15"/>
-      <c r="K94" s="15"/>
-      <c r="L94" s="15"/>
+      <c r="A94" s="16"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="17"/>
+      <c r="E94" s="17"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+      <c r="L94" s="16"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="15"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="16"/>
-      <c r="E95" s="16"/>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="15"/>
-      <c r="K95" s="15"/>
-      <c r="L95" s="15"/>
+      <c r="A95" s="16"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="17"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+      <c r="K95" s="16"/>
+      <c r="L95" s="16"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="15"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="16"/>
-      <c r="E96" s="16"/>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="15"/>
-      <c r="K96" s="15"/>
-      <c r="L96" s="15"/>
+      <c r="A96" s="16"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="17"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="16"/>
+      <c r="H96" s="16"/>
+      <c r="I96" s="16"/>
+      <c r="J96" s="16"/>
+      <c r="K96" s="16"/>
+      <c r="L96" s="16"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="15"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
-      <c r="E97" s="16"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
-      <c r="L97" s="15"/>
+      <c r="A97" s="16"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="17"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="16"/>
+      <c r="J97" s="16"/>
+      <c r="K97" s="16"/>
+      <c r="L97" s="16"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="15"/>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="15"/>
-      <c r="K98" s="15"/>
-      <c r="L98" s="15"/>
+      <c r="A98" s="16"/>
+      <c r="B98" s="17"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="17"/>
+      <c r="E98" s="17"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="16"/>
+      <c r="H98" s="16"/>
+      <c r="I98" s="16"/>
+      <c r="J98" s="16"/>
+      <c r="K98" s="16"/>
+      <c r="L98" s="16"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="15"/>
-      <c r="B99" s="16"/>
-      <c r="C99" s="16"/>
-      <c r="D99" s="16"/>
-      <c r="E99" s="16"/>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
-      <c r="H99" s="15"/>
-      <c r="I99" s="15"/>
-      <c r="J99" s="15"/>
-      <c r="K99" s="15"/>
-      <c r="L99" s="15"/>
+      <c r="A99" s="16"/>
+      <c r="B99" s="17"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="17"/>
+      <c r="E99" s="17"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="16"/>
+      <c r="H99" s="16"/>
+      <c r="I99" s="16"/>
+      <c r="J99" s="16"/>
+      <c r="K99" s="16"/>
+      <c r="L99" s="16"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="15"/>
-      <c r="B100" s="16"/>
-      <c r="C100" s="16"/>
-      <c r="D100" s="16"/>
-      <c r="E100" s="16"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
-      <c r="I100" s="15"/>
-      <c r="J100" s="15"/>
-      <c r="K100" s="15"/>
-      <c r="L100" s="15"/>
+      <c r="A100" s="16"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="17"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
+      <c r="I100" s="16"/>
+      <c r="J100" s="16"/>
+      <c r="K100" s="16"/>
+      <c r="L100" s="16"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="15"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="16"/>
-      <c r="E101" s="16"/>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="15"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="15"/>
-      <c r="K101" s="15"/>
-      <c r="L101" s="15"/>
+      <c r="A101" s="16"/>
+      <c r="B101" s="17"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+      <c r="I101" s="16"/>
+      <c r="J101" s="16"/>
+      <c r="K101" s="16"/>
+      <c r="L101" s="16"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="15"/>
-      <c r="B102" s="16"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="16"/>
-      <c r="E102" s="16"/>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
-      <c r="H102" s="15"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="15"/>
-      <c r="K102" s="15"/>
-      <c r="L102" s="15"/>
+      <c r="A102" s="16"/>
+      <c r="B102" s="17"/>
+      <c r="C102" s="17"/>
+      <c r="D102" s="17"/>
+      <c r="E102" s="17"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
+      <c r="I102" s="16"/>
+      <c r="J102" s="16"/>
+      <c r="K102" s="16"/>
+      <c r="L102" s="16"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="15"/>
-      <c r="B103" s="16"/>
-      <c r="C103" s="16"/>
-      <c r="D103" s="16"/>
-      <c r="E103" s="16"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="15"/>
-      <c r="I103" s="15"/>
-      <c r="J103" s="15"/>
-      <c r="K103" s="15"/>
-      <c r="L103" s="15"/>
+      <c r="A103" s="16"/>
+      <c r="B103" s="17"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="16"/>
+      <c r="J103" s="16"/>
+      <c r="K103" s="16"/>
+      <c r="L103" s="16"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="15"/>
-      <c r="B104" s="16"/>
-      <c r="C104" s="16"/>
-      <c r="D104" s="16"/>
-      <c r="E104" s="16"/>
-      <c r="F104" s="15"/>
-      <c r="G104" s="15"/>
-      <c r="H104" s="15"/>
-      <c r="I104" s="15"/>
-      <c r="J104" s="15"/>
-      <c r="K104" s="15"/>
-      <c r="L104" s="15"/>
+      <c r="A104" s="16"/>
+      <c r="B104" s="17"/>
+      <c r="C104" s="17"/>
+      <c r="D104" s="17"/>
+      <c r="E104" s="17"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="16"/>
+      <c r="J104" s="16"/>
+      <c r="K104" s="16"/>
+      <c r="L104" s="16"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="15"/>
-      <c r="B105" s="16"/>
-      <c r="C105" s="16"/>
-      <c r="D105" s="16"/>
-      <c r="E105" s="16"/>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15"/>
-      <c r="H105" s="15"/>
-      <c r="I105" s="15"/>
-      <c r="J105" s="15"/>
-      <c r="K105" s="15"/>
-      <c r="L105" s="15"/>
+      <c r="A105" s="16"/>
+      <c r="B105" s="17"/>
+      <c r="C105" s="17"/>
+      <c r="D105" s="17"/>
+      <c r="E105" s="17"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="16"/>
+      <c r="H105" s="16"/>
+      <c r="I105" s="16"/>
+      <c r="J105" s="16"/>
+      <c r="K105" s="16"/>
+      <c r="L105" s="16"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="15"/>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16"/>
-      <c r="D106" s="16"/>
-      <c r="E106" s="16"/>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15"/>
-      <c r="H106" s="15"/>
-      <c r="I106" s="15"/>
-      <c r="J106" s="15"/>
-      <c r="K106" s="15"/>
-      <c r="L106" s="15"/>
+      <c r="A106" s="16"/>
+      <c r="B106" s="17"/>
+      <c r="C106" s="17"/>
+      <c r="D106" s="17"/>
+      <c r="E106" s="17"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="16"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="16"/>
+      <c r="K106" s="16"/>
+      <c r="L106" s="16"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="15"/>
-      <c r="B107" s="16"/>
-      <c r="C107" s="16"/>
-      <c r="D107" s="16"/>
-      <c r="E107" s="16"/>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15"/>
-      <c r="H107" s="15"/>
-      <c r="I107" s="15"/>
-      <c r="J107" s="15"/>
-      <c r="K107" s="15"/>
-      <c r="L107" s="15"/>
+      <c r="A107" s="16"/>
+      <c r="B107" s="17"/>
+      <c r="C107" s="17"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="17"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="16"/>
+      <c r="H107" s="16"/>
+      <c r="I107" s="16"/>
+      <c r="J107" s="16"/>
+      <c r="K107" s="16"/>
+      <c r="L107" s="16"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="15"/>
-      <c r="B108" s="16"/>
-      <c r="C108" s="16"/>
-      <c r="D108" s="16"/>
-      <c r="E108" s="16"/>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15"/>
-      <c r="H108" s="15"/>
-      <c r="I108" s="15"/>
-      <c r="J108" s="15"/>
-      <c r="K108" s="15"/>
-      <c r="L108" s="15"/>
+      <c r="A108" s="16"/>
+      <c r="B108" s="17"/>
+      <c r="C108" s="17"/>
+      <c r="D108" s="17"/>
+      <c r="E108" s="17"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="16"/>
+      <c r="H108" s="16"/>
+      <c r="I108" s="16"/>
+      <c r="J108" s="16"/>
+      <c r="K108" s="16"/>
+      <c r="L108" s="16"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="15"/>
-      <c r="B109" s="16"/>
-      <c r="C109" s="16"/>
-      <c r="D109" s="16"/>
-      <c r="E109" s="16"/>
-      <c r="F109" s="15"/>
-      <c r="G109" s="15"/>
-      <c r="H109" s="15"/>
-      <c r="I109" s="15"/>
-      <c r="J109" s="15"/>
-      <c r="K109" s="15"/>
-      <c r="L109" s="15"/>
+      <c r="A109" s="16"/>
+      <c r="B109" s="17"/>
+      <c r="C109" s="17"/>
+      <c r="D109" s="17"/>
+      <c r="E109" s="17"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="16"/>
+      <c r="H109" s="16"/>
+      <c r="I109" s="16"/>
+      <c r="J109" s="16"/>
+      <c r="K109" s="16"/>
+      <c r="L109" s="16"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="15"/>
-      <c r="B110" s="16"/>
-      <c r="C110" s="16"/>
-      <c r="D110" s="16"/>
-      <c r="E110" s="16"/>
-      <c r="F110" s="15"/>
-      <c r="G110" s="15"/>
-      <c r="H110" s="15"/>
-      <c r="I110" s="15"/>
-      <c r="J110" s="15"/>
-      <c r="K110" s="15"/>
-      <c r="L110" s="15"/>
+      <c r="A110" s="16"/>
+      <c r="B110" s="17"/>
+      <c r="C110" s="17"/>
+      <c r="D110" s="17"/>
+      <c r="E110" s="17"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="16"/>
+      <c r="H110" s="16"/>
+      <c r="I110" s="16"/>
+      <c r="J110" s="16"/>
+      <c r="K110" s="16"/>
+      <c r="L110" s="16"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="15"/>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
-      <c r="D111" s="16"/>
-      <c r="E111" s="16"/>
-      <c r="F111" s="15"/>
-      <c r="G111" s="15"/>
-      <c r="H111" s="15"/>
-      <c r="I111" s="15"/>
-      <c r="J111" s="15"/>
-      <c r="K111" s="15"/>
-      <c r="L111" s="15"/>
+      <c r="A111" s="16"/>
+      <c r="B111" s="17"/>
+      <c r="C111" s="17"/>
+      <c r="D111" s="17"/>
+      <c r="E111" s="17"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="16"/>
+      <c r="J111" s="16"/>
+      <c r="K111" s="16"/>
+      <c r="L111" s="16"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="15"/>
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
-      <c r="D112" s="16"/>
-      <c r="E112" s="16"/>
-      <c r="F112" s="15"/>
-      <c r="G112" s="15"/>
-      <c r="H112" s="15"/>
-      <c r="I112" s="15"/>
-      <c r="J112" s="15"/>
-      <c r="K112" s="15"/>
-      <c r="L112" s="15"/>
+      <c r="A112" s="16"/>
+      <c r="B112" s="17"/>
+      <c r="C112" s="17"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16"/>
+      <c r="I112" s="16"/>
+      <c r="J112" s="16"/>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="15"/>
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="16"/>
-      <c r="E113" s="16"/>
-      <c r="F113" s="15"/>
-      <c r="G113" s="15"/>
-      <c r="H113" s="15"/>
-      <c r="I113" s="15"/>
-      <c r="J113" s="15"/>
-      <c r="K113" s="15"/>
-      <c r="L113" s="15"/>
+      <c r="A113" s="16"/>
+      <c r="B113" s="17"/>
+      <c r="C113" s="17"/>
+      <c r="D113" s="17"/>
+      <c r="E113" s="17"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16"/>
+      <c r="I113" s="16"/>
+      <c r="J113" s="16"/>
+      <c r="K113" s="16"/>
+      <c r="L113" s="16"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="15"/>
-      <c r="B114" s="16"/>
-      <c r="C114" s="16"/>
-      <c r="D114" s="16"/>
-      <c r="E114" s="16"/>
-      <c r="F114" s="15"/>
-      <c r="G114" s="15"/>
-      <c r="H114" s="15"/>
-      <c r="I114" s="15"/>
-      <c r="J114" s="15"/>
-      <c r="K114" s="15"/>
-      <c r="L114" s="15"/>
+      <c r="A114" s="16"/>
+      <c r="B114" s="17"/>
+      <c r="C114" s="17"/>
+      <c r="D114" s="17"/>
+      <c r="E114" s="17"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="16"/>
+      <c r="H114" s="16"/>
+      <c r="I114" s="16"/>
+      <c r="J114" s="16"/>
+      <c r="K114" s="16"/>
+      <c r="L114" s="16"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="15"/>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="15"/>
-      <c r="G115" s="15"/>
-      <c r="H115" s="15"/>
-      <c r="I115" s="15"/>
-      <c r="J115" s="15"/>
-      <c r="K115" s="15"/>
-      <c r="L115" s="15"/>
+      <c r="A115" s="16"/>
+      <c r="B115" s="17"/>
+      <c r="C115" s="17"/>
+      <c r="D115" s="17"/>
+      <c r="E115" s="17"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="16"/>
+      <c r="H115" s="16"/>
+      <c r="I115" s="16"/>
+      <c r="J115" s="16"/>
+      <c r="K115" s="16"/>
+      <c r="L115" s="16"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="15"/>
-      <c r="B116" s="16"/>
-      <c r="C116" s="16"/>
-      <c r="D116" s="16"/>
-      <c r="E116" s="16"/>
-      <c r="F116" s="15"/>
-      <c r="G116" s="15"/>
-      <c r="H116" s="15"/>
-      <c r="I116" s="15"/>
-      <c r="J116" s="15"/>
-      <c r="K116" s="15"/>
-      <c r="L116" s="15"/>
+      <c r="A116" s="16"/>
+      <c r="B116" s="17"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="17"/>
+      <c r="E116" s="17"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="16"/>
+      <c r="H116" s="16"/>
+      <c r="I116" s="16"/>
+      <c r="J116" s="16"/>
+      <c r="K116" s="16"/>
+      <c r="L116" s="16"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="15"/>
-      <c r="B117" s="16"/>
-      <c r="C117" s="16"/>
-      <c r="D117" s="16"/>
-      <c r="E117" s="16"/>
-      <c r="F117" s="15"/>
-      <c r="G117" s="15"/>
-      <c r="H117" s="15"/>
-      <c r="I117" s="15"/>
-      <c r="J117" s="15"/>
-      <c r="K117" s="15"/>
-      <c r="L117" s="15"/>
+      <c r="A117" s="16"/>
+      <c r="B117" s="17"/>
+      <c r="C117" s="17"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="17"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="16"/>
+      <c r="H117" s="16"/>
+      <c r="I117" s="16"/>
+      <c r="J117" s="16"/>
+      <c r="K117" s="16"/>
+      <c r="L117" s="16"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="15"/>
-      <c r="B118" s="16"/>
-      <c r="C118" s="16"/>
-      <c r="D118" s="16"/>
-      <c r="E118" s="16"/>
-      <c r="F118" s="15"/>
-      <c r="G118" s="15"/>
-      <c r="H118" s="15"/>
-      <c r="I118" s="15"/>
-      <c r="J118" s="15"/>
-      <c r="K118" s="15"/>
-      <c r="L118" s="15"/>
+      <c r="A118" s="16"/>
+      <c r="B118" s="17"/>
+      <c r="C118" s="17"/>
+      <c r="D118" s="17"/>
+      <c r="E118" s="17"/>
+      <c r="F118" s="16"/>
+      <c r="G118" s="16"/>
+      <c r="H118" s="16"/>
+      <c r="I118" s="16"/>
+      <c r="J118" s="16"/>
+      <c r="K118" s="16"/>
+      <c r="L118" s="16"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="15"/>
-      <c r="B119" s="16"/>
-      <c r="C119" s="16"/>
-      <c r="D119" s="16"/>
-      <c r="E119" s="16"/>
-      <c r="F119" s="15"/>
-      <c r="G119" s="15"/>
-      <c r="H119" s="15"/>
-      <c r="I119" s="15"/>
-      <c r="J119" s="15"/>
-      <c r="K119" s="15"/>
-      <c r="L119" s="15"/>
+      <c r="A119" s="16"/>
+      <c r="B119" s="17"/>
+      <c r="C119" s="17"/>
+      <c r="D119" s="17"/>
+      <c r="E119" s="17"/>
+      <c r="F119" s="16"/>
+      <c r="G119" s="16"/>
+      <c r="H119" s="16"/>
+      <c r="I119" s="16"/>
+      <c r="J119" s="16"/>
+      <c r="K119" s="16"/>
+      <c r="L119" s="16"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="15"/>
-      <c r="B120" s="16"/>
-      <c r="C120" s="16"/>
-      <c r="D120" s="16"/>
-      <c r="E120" s="16"/>
-      <c r="F120" s="15"/>
-      <c r="G120" s="15"/>
-      <c r="H120" s="15"/>
-      <c r="I120" s="15"/>
-      <c r="J120" s="15"/>
-      <c r="K120" s="15"/>
-      <c r="L120" s="15"/>
+      <c r="A120" s="16"/>
+      <c r="B120" s="17"/>
+      <c r="C120" s="17"/>
+      <c r="D120" s="17"/>
+      <c r="E120" s="17"/>
+      <c r="F120" s="16"/>
+      <c r="G120" s="16"/>
+      <c r="H120" s="16"/>
+      <c r="I120" s="16"/>
+      <c r="J120" s="16"/>
+      <c r="K120" s="16"/>
+      <c r="L120" s="16"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="15"/>
-      <c r="B121" s="16"/>
-      <c r="C121" s="16"/>
-      <c r="D121" s="16"/>
-      <c r="E121" s="16"/>
-      <c r="F121" s="15"/>
-      <c r="G121" s="15"/>
-      <c r="H121" s="15"/>
-      <c r="I121" s="15"/>
-      <c r="J121" s="15"/>
-      <c r="K121" s="15"/>
-      <c r="L121" s="15"/>
+      <c r="A121" s="16"/>
+      <c r="B121" s="17"/>
+      <c r="C121" s="17"/>
+      <c r="D121" s="17"/>
+      <c r="E121" s="17"/>
+      <c r="F121" s="16"/>
+      <c r="G121" s="16"/>
+      <c r="H121" s="16"/>
+      <c r="I121" s="16"/>
+      <c r="J121" s="16"/>
+      <c r="K121" s="16"/>
+      <c r="L121" s="16"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="15"/>
-      <c r="B122" s="16"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="16"/>
-      <c r="E122" s="16"/>
-      <c r="F122" s="15"/>
-      <c r="G122" s="15"/>
-      <c r="H122" s="15"/>
-      <c r="I122" s="15"/>
-      <c r="J122" s="15"/>
-      <c r="K122" s="15"/>
-      <c r="L122" s="15"/>
+      <c r="A122" s="16"/>
+      <c r="B122" s="17"/>
+      <c r="C122" s="17"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="16"/>
+      <c r="G122" s="16"/>
+      <c r="H122" s="16"/>
+      <c r="I122" s="16"/>
+      <c r="J122" s="16"/>
+      <c r="K122" s="16"/>
+      <c r="L122" s="16"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="15"/>
-      <c r="B123" s="16"/>
-      <c r="C123" s="16"/>
-      <c r="D123" s="16"/>
-      <c r="E123" s="16"/>
-      <c r="F123" s="15"/>
-      <c r="G123" s="15"/>
-      <c r="H123" s="15"/>
-      <c r="I123" s="15"/>
-      <c r="J123" s="15"/>
-      <c r="K123" s="15"/>
-      <c r="L123" s="15"/>
+      <c r="A123" s="16"/>
+      <c r="B123" s="17"/>
+      <c r="C123" s="17"/>
+      <c r="D123" s="17"/>
+      <c r="E123" s="17"/>
+      <c r="F123" s="16"/>
+      <c r="G123" s="16"/>
+      <c r="H123" s="16"/>
+      <c r="I123" s="16"/>
+      <c r="J123" s="16"/>
+      <c r="K123" s="16"/>
+      <c r="L123" s="16"/>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="15"/>
-      <c r="B124" s="16"/>
-      <c r="C124" s="16"/>
-      <c r="D124" s="16"/>
-      <c r="E124" s="16"/>
-      <c r="F124" s="15"/>
-      <c r="G124" s="15"/>
-      <c r="H124" s="15"/>
-      <c r="I124" s="15"/>
-      <c r="J124" s="15"/>
-      <c r="K124" s="15"/>
-      <c r="L124" s="15"/>
+      <c r="A124" s="16"/>
+      <c r="B124" s="17"/>
+      <c r="C124" s="17"/>
+      <c r="D124" s="17"/>
+      <c r="E124" s="17"/>
+      <c r="F124" s="16"/>
+      <c r="G124" s="16"/>
+      <c r="H124" s="16"/>
+      <c r="I124" s="16"/>
+      <c r="J124" s="16"/>
+      <c r="K124" s="16"/>
+      <c r="L124" s="16"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="15"/>
-      <c r="B125" s="16"/>
-      <c r="C125" s="16"/>
-      <c r="D125" s="16"/>
-      <c r="E125" s="16"/>
-      <c r="F125" s="15"/>
-      <c r="G125" s="15"/>
-      <c r="H125" s="15"/>
-      <c r="I125" s="15"/>
-      <c r="J125" s="15"/>
-      <c r="K125" s="15"/>
-      <c r="L125" s="15"/>
+      <c r="A125" s="16"/>
+      <c r="B125" s="17"/>
+      <c r="C125" s="17"/>
+      <c r="D125" s="17"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="16"/>
+      <c r="G125" s="16"/>
+      <c r="H125" s="16"/>
+      <c r="I125" s="16"/>
+      <c r="J125" s="16"/>
+      <c r="K125" s="16"/>
+      <c r="L125" s="16"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="15"/>
-      <c r="B126" s="16"/>
-      <c r="C126" s="16"/>
-      <c r="D126" s="16"/>
-      <c r="E126" s="16"/>
-      <c r="F126" s="15"/>
-      <c r="G126" s="15"/>
-      <c r="H126" s="15"/>
-      <c r="I126" s="15"/>
-      <c r="J126" s="15"/>
-      <c r="K126" s="15"/>
-      <c r="L126" s="15"/>
+      <c r="A126" s="16"/>
+      <c r="B126" s="17"/>
+      <c r="C126" s="17"/>
+      <c r="D126" s="17"/>
+      <c r="E126" s="17"/>
+      <c r="F126" s="16"/>
+      <c r="G126" s="16"/>
+      <c r="H126" s="16"/>
+      <c r="I126" s="16"/>
+      <c r="J126" s="16"/>
+      <c r="K126" s="16"/>
+      <c r="L126" s="16"/>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="15"/>
-      <c r="B127" s="16"/>
-      <c r="C127" s="16"/>
-      <c r="D127" s="16"/>
-      <c r="E127" s="16"/>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15"/>
-      <c r="H127" s="15"/>
-      <c r="I127" s="15"/>
-      <c r="J127" s="15"/>
-      <c r="K127" s="15"/>
-      <c r="L127" s="15"/>
+      <c r="A127" s="16"/>
+      <c r="B127" s="17"/>
+      <c r="C127" s="17"/>
+      <c r="D127" s="17"/>
+      <c r="E127" s="17"/>
+      <c r="F127" s="16"/>
+      <c r="G127" s="16"/>
+      <c r="H127" s="16"/>
+      <c r="I127" s="16"/>
+      <c r="J127" s="16"/>
+      <c r="K127" s="16"/>
+      <c r="L127" s="16"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="15"/>
-      <c r="B128" s="16"/>
-      <c r="C128" s="16"/>
-      <c r="D128" s="16"/>
-      <c r="E128" s="16"/>
-      <c r="F128" s="15"/>
-      <c r="G128" s="15"/>
-      <c r="H128" s="15"/>
-      <c r="I128" s="15"/>
-      <c r="J128" s="15"/>
-      <c r="K128" s="15"/>
-      <c r="L128" s="15"/>
+      <c r="A128" s="16"/>
+      <c r="B128" s="17"/>
+      <c r="C128" s="17"/>
+      <c r="D128" s="17"/>
+      <c r="E128" s="17"/>
+      <c r="F128" s="16"/>
+      <c r="G128" s="16"/>
+      <c r="H128" s="16"/>
+      <c r="I128" s="16"/>
+      <c r="J128" s="16"/>
+      <c r="K128" s="16"/>
+      <c r="L128" s="16"/>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="15"/>
-      <c r="B129" s="16"/>
-      <c r="C129" s="16"/>
-      <c r="D129" s="16"/>
-      <c r="E129" s="16"/>
-      <c r="F129" s="15"/>
-      <c r="G129" s="15"/>
-      <c r="H129" s="15"/>
-      <c r="I129" s="15"/>
-      <c r="J129" s="15"/>
-      <c r="K129" s="15"/>
-      <c r="L129" s="15"/>
+      <c r="A129" s="16"/>
+      <c r="B129" s="17"/>
+      <c r="C129" s="17"/>
+      <c r="D129" s="17"/>
+      <c r="E129" s="17"/>
+      <c r="F129" s="16"/>
+      <c r="G129" s="16"/>
+      <c r="H129" s="16"/>
+      <c r="I129" s="16"/>
+      <c r="J129" s="16"/>
+      <c r="K129" s="16"/>
+      <c r="L129" s="16"/>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="15"/>
-      <c r="B130" s="16"/>
-      <c r="C130" s="16"/>
-      <c r="D130" s="16"/>
-      <c r="E130" s="16"/>
-      <c r="F130" s="15"/>
-      <c r="G130" s="15"/>
-      <c r="H130" s="15"/>
-      <c r="I130" s="15"/>
-      <c r="J130" s="15"/>
-      <c r="K130" s="15"/>
-      <c r="L130" s="15"/>
+      <c r="A130" s="16"/>
+      <c r="B130" s="17"/>
+      <c r="C130" s="17"/>
+      <c r="D130" s="17"/>
+      <c r="E130" s="17"/>
+      <c r="F130" s="16"/>
+      <c r="G130" s="16"/>
+      <c r="H130" s="16"/>
+      <c r="I130" s="16"/>
+      <c r="J130" s="16"/>
+      <c r="K130" s="16"/>
+      <c r="L130" s="16"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="15"/>
-      <c r="B131" s="16"/>
-      <c r="C131" s="16"/>
-      <c r="D131" s="16"/>
-      <c r="E131" s="16"/>
-      <c r="F131" s="15"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="15"/>
-      <c r="I131" s="15"/>
-      <c r="J131" s="15"/>
-      <c r="K131" s="15"/>
-      <c r="L131" s="15"/>
+      <c r="A131" s="16"/>
+      <c r="B131" s="17"/>
+      <c r="C131" s="17"/>
+      <c r="D131" s="17"/>
+      <c r="E131" s="17"/>
+      <c r="F131" s="16"/>
+      <c r="G131" s="16"/>
+      <c r="H131" s="16"/>
+      <c r="I131" s="16"/>
+      <c r="J131" s="16"/>
+      <c r="K131" s="16"/>
+      <c r="L131" s="16"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="15"/>
-      <c r="B132" s="16"/>
-      <c r="C132" s="16"/>
-      <c r="D132" s="16"/>
-      <c r="E132" s="16"/>
-      <c r="F132" s="15"/>
-      <c r="G132" s="15"/>
-      <c r="H132" s="15"/>
-      <c r="I132" s="15"/>
-      <c r="J132" s="15"/>
-      <c r="K132" s="15"/>
-      <c r="L132" s="15"/>
+      <c r="A132" s="16"/>
+      <c r="B132" s="17"/>
+      <c r="C132" s="17"/>
+      <c r="D132" s="17"/>
+      <c r="E132" s="17"/>
+      <c r="F132" s="16"/>
+      <c r="G132" s="16"/>
+      <c r="H132" s="16"/>
+      <c r="I132" s="16"/>
+      <c r="J132" s="16"/>
+      <c r="K132" s="16"/>
+      <c r="L132" s="16"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="15"/>
-      <c r="B133" s="16"/>
-      <c r="C133" s="16"/>
-      <c r="D133" s="16"/>
-      <c r="E133" s="16"/>
-      <c r="F133" s="15"/>
-      <c r="G133" s="15"/>
-      <c r="H133" s="15"/>
-      <c r="I133" s="15"/>
-      <c r="J133" s="15"/>
-      <c r="K133" s="15"/>
-      <c r="L133" s="15"/>
+      <c r="A133" s="16"/>
+      <c r="B133" s="17"/>
+      <c r="C133" s="17"/>
+      <c r="D133" s="17"/>
+      <c r="E133" s="17"/>
+      <c r="F133" s="16"/>
+      <c r="G133" s="16"/>
+      <c r="H133" s="16"/>
+      <c r="I133" s="16"/>
+      <c r="J133" s="16"/>
+      <c r="K133" s="16"/>
+      <c r="L133" s="16"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="15"/>
-      <c r="B134" s="16"/>
-      <c r="C134" s="16"/>
-      <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
-      <c r="F134" s="15"/>
-      <c r="G134" s="15"/>
-      <c r="H134" s="15"/>
-      <c r="I134" s="15"/>
-      <c r="J134" s="15"/>
-      <c r="K134" s="15"/>
-      <c r="L134" s="15"/>
+      <c r="A134" s="16"/>
+      <c r="B134" s="17"/>
+      <c r="C134" s="17"/>
+      <c r="D134" s="17"/>
+      <c r="E134" s="17"/>
+      <c r="F134" s="16"/>
+      <c r="G134" s="16"/>
+      <c r="H134" s="16"/>
+      <c r="I134" s="16"/>
+      <c r="J134" s="16"/>
+      <c r="K134" s="16"/>
+      <c r="L134" s="16"/>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="15"/>
-      <c r="B135" s="16"/>
-      <c r="C135" s="16"/>
-      <c r="D135" s="16"/>
-      <c r="E135" s="16"/>
-      <c r="F135" s="15"/>
-      <c r="G135" s="15"/>
-      <c r="H135" s="15"/>
-      <c r="I135" s="15"/>
-      <c r="J135" s="15"/>
-      <c r="K135" s="15"/>
-      <c r="L135" s="15"/>
+      <c r="A135" s="16"/>
+      <c r="B135" s="17"/>
+      <c r="C135" s="17"/>
+      <c r="D135" s="17"/>
+      <c r="E135" s="17"/>
+      <c r="F135" s="16"/>
+      <c r="G135" s="16"/>
+      <c r="H135" s="16"/>
+      <c r="I135" s="16"/>
+      <c r="J135" s="16"/>
+      <c r="K135" s="16"/>
+      <c r="L135" s="16"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="15"/>
-      <c r="B136" s="16"/>
-      <c r="C136" s="16"/>
-      <c r="D136" s="16"/>
-      <c r="E136" s="16"/>
-      <c r="F136" s="15"/>
-      <c r="G136" s="15"/>
-      <c r="H136" s="15"/>
-      <c r="I136" s="15"/>
-      <c r="J136" s="15"/>
-      <c r="K136" s="15"/>
-      <c r="L136" s="15"/>
+      <c r="A136" s="16"/>
+      <c r="B136" s="17"/>
+      <c r="C136" s="17"/>
+      <c r="D136" s="17"/>
+      <c r="E136" s="17"/>
+      <c r="F136" s="16"/>
+      <c r="G136" s="16"/>
+      <c r="H136" s="16"/>
+      <c r="I136" s="16"/>
+      <c r="J136" s="16"/>
+      <c r="K136" s="16"/>
+      <c r="L136" s="16"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="15"/>
-      <c r="B137" s="16"/>
-      <c r="C137" s="16"/>
-      <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="15"/>
-      <c r="G137" s="15"/>
-      <c r="H137" s="15"/>
-      <c r="I137" s="15"/>
-      <c r="J137" s="15"/>
-      <c r="K137" s="15"/>
-      <c r="L137" s="15"/>
+      <c r="A137" s="16"/>
+      <c r="B137" s="17"/>
+      <c r="C137" s="17"/>
+      <c r="D137" s="17"/>
+      <c r="E137" s="17"/>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
+      <c r="H137" s="16"/>
+      <c r="I137" s="16"/>
+      <c r="J137" s="16"/>
+      <c r="K137" s="16"/>
+      <c r="L137" s="16"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="15"/>
-      <c r="B138" s="16"/>
-      <c r="C138" s="16"/>
-      <c r="D138" s="16"/>
-      <c r="E138" s="16"/>
-      <c r="F138" s="15"/>
-      <c r="G138" s="15"/>
-      <c r="H138" s="15"/>
-      <c r="I138" s="15"/>
-      <c r="J138" s="15"/>
-      <c r="K138" s="15"/>
-      <c r="L138" s="15"/>
+      <c r="A138" s="16"/>
+      <c r="B138" s="17"/>
+      <c r="C138" s="17"/>
+      <c r="D138" s="17"/>
+      <c r="E138" s="17"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="16"/>
+      <c r="H138" s="16"/>
+      <c r="I138" s="16"/>
+      <c r="J138" s="16"/>
+      <c r="K138" s="16"/>
+      <c r="L138" s="16"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="15"/>
-      <c r="B139" s="16"/>
-      <c r="C139" s="16"/>
-      <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="15"/>
-      <c r="G139" s="15"/>
-      <c r="H139" s="15"/>
-      <c r="I139" s="15"/>
-      <c r="J139" s="15"/>
-      <c r="K139" s="15"/>
-      <c r="L139" s="15"/>
+      <c r="A139" s="16"/>
+      <c r="B139" s="17"/>
+      <c r="C139" s="17"/>
+      <c r="D139" s="17"/>
+      <c r="E139" s="17"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="16"/>
+      <c r="H139" s="16"/>
+      <c r="I139" s="16"/>
+      <c r="J139" s="16"/>
+      <c r="K139" s="16"/>
+      <c r="L139" s="16"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="15"/>
-      <c r="B140" s="16"/>
-      <c r="C140" s="16"/>
-      <c r="D140" s="16"/>
-      <c r="E140" s="16"/>
-      <c r="F140" s="15"/>
-      <c r="G140" s="15"/>
-      <c r="H140" s="15"/>
-      <c r="I140" s="15"/>
-      <c r="J140" s="15"/>
-      <c r="K140" s="15"/>
-      <c r="L140" s="15"/>
+      <c r="A140" s="16"/>
+      <c r="B140" s="17"/>
+      <c r="C140" s="17"/>
+      <c r="D140" s="17"/>
+      <c r="E140" s="17"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
+      <c r="H140" s="16"/>
+      <c r="I140" s="16"/>
+      <c r="J140" s="16"/>
+      <c r="K140" s="16"/>
+      <c r="L140" s="16"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="15"/>
-      <c r="B141" s="16"/>
-      <c r="C141" s="16"/>
-      <c r="D141" s="16"/>
-      <c r="E141" s="16"/>
-      <c r="F141" s="15"/>
-      <c r="G141" s="15"/>
-      <c r="H141" s="15"/>
-      <c r="I141" s="15"/>
-      <c r="J141" s="15"/>
-      <c r="K141" s="15"/>
-      <c r="L141" s="15"/>
+      <c r="A141" s="16"/>
+      <c r="B141" s="17"/>
+      <c r="C141" s="17"/>
+      <c r="D141" s="17"/>
+      <c r="E141" s="17"/>
+      <c r="F141" s="16"/>
+      <c r="G141" s="16"/>
+      <c r="H141" s="16"/>
+      <c r="I141" s="16"/>
+      <c r="J141" s="16"/>
+      <c r="K141" s="16"/>
+      <c r="L141" s="16"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="15"/>
-      <c r="B142" s="16"/>
-      <c r="C142" s="16"/>
-      <c r="D142" s="16"/>
-      <c r="E142" s="16"/>
-      <c r="F142" s="15"/>
-      <c r="G142" s="15"/>
-      <c r="H142" s="15"/>
-      <c r="I142" s="15"/>
-      <c r="J142" s="15"/>
-      <c r="K142" s="15"/>
-      <c r="L142" s="15"/>
+      <c r="A142" s="16"/>
+      <c r="B142" s="17"/>
+      <c r="C142" s="17"/>
+      <c r="D142" s="17"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="16"/>
+      <c r="G142" s="16"/>
+      <c r="H142" s="16"/>
+      <c r="I142" s="16"/>
+      <c r="J142" s="16"/>
+      <c r="K142" s="16"/>
+      <c r="L142" s="16"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="15"/>
-      <c r="B143" s="16"/>
-      <c r="C143" s="16"/>
-      <c r="D143" s="16"/>
-      <c r="E143" s="16"/>
-      <c r="F143" s="15"/>
-      <c r="G143" s="15"/>
-      <c r="H143" s="15"/>
-      <c r="I143" s="15"/>
-      <c r="J143" s="15"/>
-      <c r="K143" s="15"/>
-      <c r="L143" s="15"/>
+      <c r="A143" s="16"/>
+      <c r="B143" s="17"/>
+      <c r="C143" s="17"/>
+      <c r="D143" s="17"/>
+      <c r="E143" s="17"/>
+      <c r="F143" s="16"/>
+      <c r="G143" s="16"/>
+      <c r="H143" s="16"/>
+      <c r="I143" s="16"/>
+      <c r="J143" s="16"/>
+      <c r="K143" s="16"/>
+      <c r="L143" s="16"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="15"/>
-      <c r="B144" s="16"/>
-      <c r="C144" s="16"/>
-      <c r="D144" s="16"/>
-      <c r="E144" s="16"/>
-      <c r="F144" s="15"/>
-      <c r="G144" s="15"/>
-      <c r="H144" s="15"/>
-      <c r="I144" s="15"/>
-      <c r="J144" s="15"/>
-      <c r="K144" s="15"/>
-      <c r="L144" s="15"/>
+      <c r="A144" s="16"/>
+      <c r="B144" s="17"/>
+      <c r="C144" s="17"/>
+      <c r="D144" s="17"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="16"/>
+      <c r="G144" s="16"/>
+      <c r="H144" s="16"/>
+      <c r="I144" s="16"/>
+      <c r="J144" s="16"/>
+      <c r="K144" s="16"/>
+      <c r="L144" s="16"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="15"/>
-      <c r="B145" s="16"/>
-      <c r="C145" s="16"/>
-      <c r="D145" s="16"/>
-      <c r="E145" s="16"/>
-      <c r="F145" s="15"/>
-      <c r="G145" s="15"/>
-      <c r="H145" s="15"/>
-      <c r="I145" s="15"/>
-      <c r="J145" s="15"/>
-      <c r="K145" s="15"/>
-      <c r="L145" s="15"/>
+      <c r="A145" s="16"/>
+      <c r="B145" s="17"/>
+      <c r="C145" s="17"/>
+      <c r="D145" s="17"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="16"/>
+      <c r="G145" s="16"/>
+      <c r="H145" s="16"/>
+      <c r="I145" s="16"/>
+      <c r="J145" s="16"/>
+      <c r="K145" s="16"/>
+      <c r="L145" s="16"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="15"/>
-      <c r="B146" s="16"/>
-      <c r="C146" s="16"/>
-      <c r="D146" s="16"/>
-      <c r="E146" s="16"/>
-      <c r="F146" s="15"/>
-      <c r="G146" s="15"/>
-      <c r="H146" s="15"/>
-      <c r="I146" s="15"/>
-      <c r="J146" s="15"/>
-      <c r="K146" s="15"/>
-      <c r="L146" s="15"/>
+      <c r="A146" s="16"/>
+      <c r="B146" s="17"/>
+      <c r="C146" s="17"/>
+      <c r="D146" s="17"/>
+      <c r="E146" s="17"/>
+      <c r="F146" s="16"/>
+      <c r="G146" s="16"/>
+      <c r="H146" s="16"/>
+      <c r="I146" s="16"/>
+      <c r="J146" s="16"/>
+      <c r="K146" s="16"/>
+      <c r="L146" s="16"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="15"/>
-      <c r="B147" s="16"/>
-      <c r="C147" s="16"/>
-      <c r="D147" s="16"/>
-      <c r="E147" s="16"/>
-      <c r="F147" s="15"/>
-      <c r="G147" s="15"/>
-      <c r="H147" s="15"/>
-      <c r="I147" s="15"/>
-      <c r="J147" s="15"/>
-      <c r="K147" s="15"/>
-      <c r="L147" s="15"/>
+      <c r="A147" s="16"/>
+      <c r="B147" s="17"/>
+      <c r="C147" s="17"/>
+      <c r="D147" s="17"/>
+      <c r="E147" s="17"/>
+      <c r="F147" s="16"/>
+      <c r="G147" s="16"/>
+      <c r="H147" s="16"/>
+      <c r="I147" s="16"/>
+      <c r="J147" s="16"/>
+      <c r="K147" s="16"/>
+      <c r="L147" s="16"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="15"/>
-      <c r="B148" s="16"/>
-      <c r="C148" s="16"/>
-      <c r="D148" s="16"/>
-      <c r="E148" s="16"/>
-      <c r="F148" s="15"/>
-      <c r="G148" s="15"/>
-      <c r="H148" s="15"/>
-      <c r="I148" s="15"/>
-      <c r="J148" s="15"/>
-      <c r="K148" s="15"/>
-      <c r="L148" s="15"/>
+      <c r="A148" s="16"/>
+      <c r="B148" s="17"/>
+      <c r="C148" s="17"/>
+      <c r="D148" s="17"/>
+      <c r="E148" s="17"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
+      <c r="H148" s="16"/>
+      <c r="I148" s="16"/>
+      <c r="J148" s="16"/>
+      <c r="K148" s="16"/>
+      <c r="L148" s="16"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="15"/>
-      <c r="B149" s="16"/>
-      <c r="C149" s="16"/>
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="15"/>
-      <c r="G149" s="15"/>
-      <c r="H149" s="15"/>
-      <c r="I149" s="15"/>
-      <c r="J149" s="15"/>
-      <c r="K149" s="15"/>
-      <c r="L149" s="15"/>
+      <c r="A149" s="16"/>
+      <c r="B149" s="17"/>
+      <c r="C149" s="17"/>
+      <c r="D149" s="17"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
+      <c r="H149" s="16"/>
+      <c r="I149" s="16"/>
+      <c r="J149" s="16"/>
+      <c r="K149" s="16"/>
+      <c r="L149" s="16"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="15"/>
-      <c r="B150" s="16"/>
-      <c r="C150" s="16"/>
-      <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
-      <c r="F150" s="15"/>
-      <c r="G150" s="15"/>
-      <c r="H150" s="15"/>
-      <c r="I150" s="15"/>
-      <c r="J150" s="15"/>
-      <c r="K150" s="15"/>
-      <c r="L150" s="15"/>
+      <c r="A150" s="16"/>
+      <c r="B150" s="17"/>
+      <c r="C150" s="17"/>
+      <c r="D150" s="17"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="16"/>
+      <c r="G150" s="16"/>
+      <c r="H150" s="16"/>
+      <c r="I150" s="16"/>
+      <c r="J150" s="16"/>
+      <c r="K150" s="16"/>
+      <c r="L150" s="16"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="15"/>
-      <c r="B151" s="16"/>
-      <c r="C151" s="16"/>
-      <c r="D151" s="16"/>
-      <c r="E151" s="16"/>
-      <c r="F151" s="15"/>
-      <c r="G151" s="15"/>
-      <c r="H151" s="15"/>
-      <c r="I151" s="15"/>
-      <c r="J151" s="15"/>
-      <c r="K151" s="15"/>
-      <c r="L151" s="15"/>
+      <c r="A151" s="16"/>
+      <c r="B151" s="17"/>
+      <c r="C151" s="17"/>
+      <c r="D151" s="17"/>
+      <c r="E151" s="17"/>
+      <c r="F151" s="16"/>
+      <c r="G151" s="16"/>
+      <c r="H151" s="16"/>
+      <c r="I151" s="16"/>
+      <c r="J151" s="16"/>
+      <c r="K151" s="16"/>
+      <c r="L151" s="16"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="15"/>
-      <c r="B152" s="16"/>
-      <c r="C152" s="16"/>
-      <c r="D152" s="16"/>
-      <c r="E152" s="16"/>
-      <c r="F152" s="15"/>
-      <c r="G152" s="15"/>
-      <c r="H152" s="15"/>
-      <c r="I152" s="15"/>
-      <c r="J152" s="15"/>
-      <c r="K152" s="15"/>
-      <c r="L152" s="15"/>
+      <c r="A152" s="16"/>
+      <c r="B152" s="17"/>
+      <c r="C152" s="17"/>
+      <c r="D152" s="17"/>
+      <c r="E152" s="17"/>
+      <c r="F152" s="16"/>
+      <c r="G152" s="16"/>
+      <c r="H152" s="16"/>
+      <c r="I152" s="16"/>
+      <c r="J152" s="16"/>
+      <c r="K152" s="16"/>
+      <c r="L152" s="16"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="15"/>
-      <c r="B153" s="16"/>
-      <c r="C153" s="16"/>
-      <c r="D153" s="16"/>
-      <c r="E153" s="16"/>
-      <c r="F153" s="15"/>
-      <c r="G153" s="15"/>
-      <c r="H153" s="15"/>
-      <c r="I153" s="15"/>
-      <c r="J153" s="15"/>
-      <c r="K153" s="15"/>
-      <c r="L153" s="15"/>
+      <c r="A153" s="16"/>
+      <c r="B153" s="17"/>
+      <c r="C153" s="17"/>
+      <c r="D153" s="17"/>
+      <c r="E153" s="17"/>
+      <c r="F153" s="16"/>
+      <c r="G153" s="16"/>
+      <c r="H153" s="16"/>
+      <c r="I153" s="16"/>
+      <c r="J153" s="16"/>
+      <c r="K153" s="16"/>
+      <c r="L153" s="16"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="15"/>
-      <c r="B154" s="16"/>
-      <c r="C154" s="16"/>
-      <c r="D154" s="16"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="15"/>
-      <c r="G154" s="15"/>
-      <c r="H154" s="15"/>
-      <c r="I154" s="15"/>
-      <c r="J154" s="15"/>
-      <c r="K154" s="15"/>
-      <c r="L154" s="15"/>
+      <c r="A154" s="16"/>
+      <c r="B154" s="17"/>
+      <c r="C154" s="17"/>
+      <c r="D154" s="17"/>
+      <c r="E154" s="17"/>
+      <c r="F154" s="16"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="16"/>
+      <c r="I154" s="16"/>
+      <c r="J154" s="16"/>
+      <c r="K154" s="16"/>
+      <c r="L154" s="16"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="15"/>
-      <c r="B155" s="16"/>
-      <c r="C155" s="16"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="15"/>
-      <c r="G155" s="15"/>
-      <c r="H155" s="15"/>
-      <c r="I155" s="15"/>
-      <c r="J155" s="15"/>
-      <c r="K155" s="15"/>
-      <c r="L155" s="15"/>
+      <c r="A155" s="16"/>
+      <c r="B155" s="17"/>
+      <c r="C155" s="17"/>
+      <c r="D155" s="17"/>
+      <c r="E155" s="17"/>
+      <c r="F155" s="16"/>
+      <c r="G155" s="16"/>
+      <c r="H155" s="16"/>
+      <c r="I155" s="16"/>
+      <c r="J155" s="16"/>
+      <c r="K155" s="16"/>
+      <c r="L155" s="16"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="15"/>
-      <c r="B156" s="16"/>
-      <c r="C156" s="16"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="15"/>
-      <c r="G156" s="15"/>
-      <c r="H156" s="15"/>
-      <c r="I156" s="15"/>
-      <c r="J156" s="15"/>
-      <c r="K156" s="15"/>
-      <c r="L156" s="15"/>
+      <c r="A156" s="16"/>
+      <c r="B156" s="17"/>
+      <c r="C156" s="17"/>
+      <c r="D156" s="17"/>
+      <c r="E156" s="17"/>
+      <c r="F156" s="16"/>
+      <c r="G156" s="16"/>
+      <c r="H156" s="16"/>
+      <c r="I156" s="16"/>
+      <c r="J156" s="16"/>
+      <c r="K156" s="16"/>
+      <c r="L156" s="16"/>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="15"/>
-      <c r="B157" s="16"/>
-      <c r="C157" s="16"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="15"/>
-      <c r="G157" s="15"/>
-      <c r="H157" s="15"/>
-      <c r="I157" s="15"/>
-      <c r="J157" s="15"/>
-      <c r="K157" s="15"/>
-      <c r="L157" s="15"/>
+      <c r="A157" s="16"/>
+      <c r="B157" s="17"/>
+      <c r="C157" s="17"/>
+      <c r="D157" s="17"/>
+      <c r="E157" s="17"/>
+      <c r="F157" s="16"/>
+      <c r="G157" s="16"/>
+      <c r="H157" s="16"/>
+      <c r="I157" s="16"/>
+      <c r="J157" s="16"/>
+      <c r="K157" s="16"/>
+      <c r="L157" s="16"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="15"/>
-      <c r="B158" s="16"/>
-      <c r="C158" s="16"/>
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="15"/>
-      <c r="G158" s="15"/>
-      <c r="H158" s="15"/>
-      <c r="I158" s="15"/>
-      <c r="J158" s="15"/>
-      <c r="K158" s="15"/>
-      <c r="L158" s="15"/>
+      <c r="A158" s="16"/>
+      <c r="B158" s="17"/>
+      <c r="C158" s="17"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="17"/>
+      <c r="F158" s="16"/>
+      <c r="G158" s="16"/>
+      <c r="H158" s="16"/>
+      <c r="I158" s="16"/>
+      <c r="J158" s="16"/>
+      <c r="K158" s="16"/>
+      <c r="L158" s="16"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="15"/>
-      <c r="B159" s="16"/>
-      <c r="C159" s="16"/>
-      <c r="D159" s="16"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="15"/>
-      <c r="G159" s="15"/>
-      <c r="H159" s="15"/>
-      <c r="I159" s="15"/>
-      <c r="J159" s="15"/>
-      <c r="K159" s="15"/>
-      <c r="L159" s="15"/>
+      <c r="A159" s="16"/>
+      <c r="B159" s="17"/>
+      <c r="C159" s="17"/>
+      <c r="D159" s="17"/>
+      <c r="E159" s="17"/>
+      <c r="F159" s="16"/>
+      <c r="G159" s="16"/>
+      <c r="H159" s="16"/>
+      <c r="I159" s="16"/>
+      <c r="J159" s="16"/>
+      <c r="K159" s="16"/>
+      <c r="L159" s="16"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="15"/>
-      <c r="B160" s="16"/>
-      <c r="C160" s="16"/>
-      <c r="D160" s="16"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="15"/>
-      <c r="G160" s="15"/>
-      <c r="H160" s="15"/>
-      <c r="I160" s="15"/>
-      <c r="J160" s="15"/>
-      <c r="K160" s="15"/>
-      <c r="L160" s="15"/>
+      <c r="A160" s="16"/>
+      <c r="B160" s="17"/>
+      <c r="C160" s="17"/>
+      <c r="D160" s="17"/>
+      <c r="E160" s="17"/>
+      <c r="F160" s="16"/>
+      <c r="G160" s="16"/>
+      <c r="H160" s="16"/>
+      <c r="I160" s="16"/>
+      <c r="J160" s="16"/>
+      <c r="K160" s="16"/>
+      <c r="L160" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M60"/>
@@ -8147,210 +9199,210 @@
         <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>264</v>
+        <v>382</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>139</v>
+        <v>257</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>143</v>
+        <v>261</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>265</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>266</v>
+        <v>384</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+        <v>385</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="1" t="s">
-        <v>268</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>269</v>
+        <v>387</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+        <v>388</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="1" t="s">
-        <v>271</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="18"/>
+        <v>391</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="19"/>
       <c r="I4" s="1" t="s">
-        <v>274</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+        <v>394</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="1" t="s">
-        <v>277</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>278</v>
+        <v>396</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
+        <v>397</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
       <c r="I6" s="1" t="s">
-        <v>280</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>281</v>
+        <v>399</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+        <v>400</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
       <c r="I7" s="1" t="s">
-        <v>283</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+        <v>403</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
       <c r="I8" s="1" t="s">
-        <v>286</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>287</v>
+        <v>405</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
+        <v>406</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
       <c r="I9" s="1" t="s">
-        <v>289</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>290</v>
+        <v>408</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
       <c r="I10" s="1" t="s">
-        <v>292</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>293</v>
+        <v>411</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18" t="n">
+        <v>412</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>295</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -8395,39 +9447,39 @@
         <v>3</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>139</v>
+        <v>257</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>143</v>
+        <v>261</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>296</v>
+        <v>414</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>297</v>
+        <v>415</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>298</v>
+        <v>416</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>299</v>
+        <v>417</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>2</v>
@@ -8440,15 +9492,15 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="1" t="s">
-        <v>300</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>301</v>
+        <v>419</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>302</v>
+        <v>420</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -8461,15 +9513,15 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="1" t="s">
-        <v>303</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>422</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>423</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -8482,15 +9534,15 @@
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="1" t="s">
-        <v>306</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>307</v>
+        <v>425</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>308</v>
+        <v>426</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -8503,15 +9555,15 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="1" t="s">
-        <v>309</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>310</v>
+        <v>428</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>311</v>
+        <v>429</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -8526,15 +9578,15 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="1" t="s">
-        <v>312</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>313</v>
+        <v>431</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>314</v>
+        <v>432</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1</v>
@@ -8549,15 +9601,15 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="1" t="s">
-        <v>315</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>316</v>
+        <v>434</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>317</v>
+        <v>435</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -8570,15 +9622,15 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="1" t="s">
-        <v>318</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>319</v>
+        <v>437</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>320</v>
+        <v>438</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -8591,15 +9643,15 @@
         <v>1</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>321</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>323</v>
+        <v>441</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -8612,15 +9664,15 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="1" t="s">
-        <v>324</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>325</v>
+        <v>443</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>326</v>
+        <v>444</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -8635,15 +9687,15 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="1" t="s">
-        <v>327</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>328</v>
+        <v>446</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>329</v>
+        <v>447</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="n">
@@ -8656,7 +9708,7 @@
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="1" t="s">
-        <v>330</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
